--- a/packages/calculators/src/modules/test/4.1-beef.xlsx
+++ b/packages/calculators/src/modules/test/4.1-beef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{D7C6FCB2-875D-AA46-9D2D-92010A8D90F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{B52FBB0C-CCFB-6442-BDD1-71F841E20C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2500" yWindow="880" windowWidth="45460" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51220" yWindow="11700" windowWidth="28800" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.2.1 methane" sheetId="2" r:id="rId1"/>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AE11">
         <f>SUM(Q11:R50)</f>
-        <v>516.07877126485812</v>
+        <v>518.72416560985539</v>
       </c>
       <c r="AF11">
         <f>$AS$8</f>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AG11">
         <f>AE11 * AF11 * 10^-3</f>
-        <v>14.450205595416028</v>
+        <v>14.524276637075952</v>
       </c>
     </row>
     <row r="12" spans="1:53" x14ac:dyDescent="0.2">
@@ -2119,38 +2119,38 @@
         <v>0.3</v>
       </c>
       <c r="J27">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <v>1.3</v>
       </c>
       <c r="L27">
         <f>(J27*K27)+(1 - J27)</f>
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="M27">
-        <f t="shared" si="0"/>
-        <v>9.309296640996001</v>
+        <f>(1.185 + 0.00454 * H27 - 0.0000026 * H27^2 + 0.315 * I27)^2 * L27</f>
+        <v>10.001723663880002</v>
       </c>
       <c r="N27">
         <f>(M27 * (1 -S$11) + (0.04 * M27)) * ( 1 - AD$11 )</f>
-        <v>3.8317064974339536</v>
+        <v>4.1167094600530074</v>
       </c>
       <c r="O27">
         <f t="shared" si="1"/>
-        <v>1.8027044885303512E-4</v>
+        <v>1.9367899463549227E-4</v>
       </c>
       <c r="P27">
         <f t="shared" si="2"/>
-        <v>2.1583064698294891E-3</v>
+        <v>2.3188416618002772E-3</v>
       </c>
       <c r="Q27">
         <f t="shared" si="3"/>
-        <v>1.6449678457839456</v>
+        <v>1.7673208260488671</v>
       </c>
       <c r="R27">
         <f t="shared" si="4"/>
-        <v>19.694546537194089</v>
+        <v>21.159430163927528</v>
       </c>
       <c r="BB27" s="2"/>
       <c r="BC27" s="2"/>
@@ -2336,38 +2336,38 @@
         <v>0.3</v>
       </c>
       <c r="J31">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K31">
         <v>1.3</v>
       </c>
       <c r="L31">
         <f t="shared" si="5"/>
-        <v>1.1800000000000002</v>
+        <v>1.3</v>
       </c>
       <c r="M31">
         <f t="shared" si="0"/>
-        <v>9.0784876333680025</v>
+        <v>10.001723663880002</v>
       </c>
       <c r="N31">
         <f>(M31 * (1 -S$11) + (0.04 * M31)) * ( 1 - AD$11 )</f>
-        <v>3.7367055098942692</v>
+        <v>4.1167094600530074</v>
       </c>
       <c r="O31">
         <f t="shared" si="1"/>
-        <v>1.7580093359221608E-4</v>
+        <v>1.9367899463549227E-4</v>
       </c>
       <c r="P31">
         <f t="shared" si="2"/>
-        <v>2.1047947391725596E-3</v>
+        <v>2.3188416618002772E-3</v>
       </c>
       <c r="Q31">
         <f t="shared" si="3"/>
-        <v>0.80209175951448586</v>
+        <v>0.88366041302443354</v>
       </c>
       <c r="R31">
         <f t="shared" si="4"/>
-        <v>9.6031259974748036</v>
+        <v>10.579715081963764</v>
       </c>
       <c r="BB31" s="2"/>
       <c r="BC31" s="2"/>

--- a/packages/calculators/src/modules/test/4.1-beef.xlsx
+++ b/packages/calculators/src/modules/test/4.1-beef.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{B52FBB0C-CCFB-6442-BDD1-71F841E20C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{F23B3008-F8F0-494C-992D-7D101CAF2D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51220" yWindow="11700" windowWidth="28800" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="119">
   <si>
     <t>(LCijkl=5 * FAijkl=5) + (1 - LCijkl=5 )</t>
   </si>
@@ -401,6 +401,18 @@
   </si>
   <si>
     <t>Mmm=14</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Missing classes</t>
+  </si>
+  <si>
+    <t>Method 2 inputs</t>
+  </si>
+  <si>
+    <t>Partial calving</t>
   </si>
 </sst>
 </file>
@@ -807,9 +819,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98CEB378-B254-8645-A19B-7F7E967AA90B}">
-  <dimension ref="A5:BF162"/>
+  <dimension ref="A5:BF180"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
     <col min="2" max="2" width="20.1640625" customWidth="1"/>
     <col min="5" max="6" width="15.83203125" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
@@ -3258,7 +3271,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="49" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.2">
       <c r="F49" t="s">
         <v>56</v>
       </c>
@@ -3332,7 +3345,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="50" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.2">
       <c r="F50" t="s">
         <v>57</v>
       </c>
@@ -3406,7 +3419,122 @@
         <v>460</v>
       </c>
     </row>
-    <row r="51" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" t="s">
+        <v>54</v>
+      </c>
+      <c r="G51">
+        <v>100</v>
+      </c>
+      <c r="H51" cm="1">
+        <f t="array" ref="H51:H54">_xlfn.XLOOKUP(E51, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>80</v>
+      </c>
+      <c r="I51" cm="1">
+        <f t="array" ref="I51:I54">_xlfn.XLOOKUP(E51, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.5</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <f>(1.185 + 0.00454 * H51 - 0.0000026 * H51^2 + 0.315 * I51)^2 * L51</f>
+        <v>2.8529236835999998</v>
+      </c>
+      <c r="N51">
+        <f>(M51 * (1 -S51) + (0.04 * M51)) * ( 1 - AD$11 )</f>
+        <v>1.1742633881697597</v>
+      </c>
+      <c r="O51">
+        <f>N51 * AB$51 * X$51 * Z$51 * AC$51</f>
+        <v>5.5245616593758213E-5</v>
+      </c>
+      <c r="P51">
+        <f>N51 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>6.6143382058828331E-4</v>
+      </c>
+      <c r="Q51">
+        <f>G51*O51*91.25</f>
+        <v>0.50411625141804373</v>
+      </c>
+      <c r="R51">
+        <f>G51*P51*91.25</f>
+        <v>6.0355836128680851</v>
+      </c>
+      <c r="S51" cm="1">
+        <f t="array" ref="S51:V51">_xlfn.XLOOKUP(C51,$AR$18:$AR$26,$AS$18:$AV$26)</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T51">
+        <v>0.65</v>
+      </c>
+      <c r="U51">
+        <v>0.6</v>
+      </c>
+      <c r="V51">
+        <v>0.5</v>
+      </c>
+      <c r="W51" t="s">
+        <v>91</v>
+      </c>
+      <c r="X51">
+        <f>IF(W51="yes", $AN$6, $AO$6)</f>
+        <v>0.05</v>
+      </c>
+      <c r="Y51">
+        <f>IF(W51="yes", $AN$7, $AO$7)</f>
+        <v>0.95</v>
+      </c>
+      <c r="Z51">
+        <f>VLOOKUP(B51, $AZ$17:$BA$26, 2, FALSE)</f>
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="AA51">
+        <f>$BA$14</f>
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="AB51">
+        <f>$AS$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="AC51">
+        <f>$AS$6</f>
+        <v>0.6784</v>
+      </c>
+      <c r="AD51">
+        <f>$AS$7</f>
+        <v>0.16</v>
+      </c>
+      <c r="AE51">
+        <f>SUM(Q51:R90)</f>
+        <v>204.8566346624763</v>
+      </c>
+      <c r="AF51">
+        <f>$AS$8</f>
+        <v>28</v>
+      </c>
+      <c r="AG51">
+        <f>AE51 * AF51 * 10^-3</f>
+        <v>5.7359857705493358</v>
+      </c>
       <c r="AM51" t="s">
         <v>59</v>
       </c>
@@ -3444,7 +3572,46 @@
         <v>420</v>
       </c>
     </row>
-    <row r="52" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F52" t="s">
+        <v>55</v>
+      </c>
+      <c r="G52">
+        <v>110</v>
+      </c>
+      <c r="H52">
+        <v>170</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <f t="shared" ref="M52:M66" si="6">(1.185 + 0.00454 * H52 - 0.0000026 * H52^2 + 0.315 * I52)^2 * L52</f>
+        <v>4.8253151556000002</v>
+      </c>
+      <c r="N52">
+        <f>(M52 * (1 -T$11) + (0.04 * M52)) * ( 1 - AD$11 )</f>
+        <v>1.58077324497456</v>
+      </c>
+      <c r="O52">
+        <f t="shared" ref="O52:O90" si="7">N52 * AB$51 * X$51 * Z$51 * AC$51</f>
+        <v>7.4370702087247912E-5</v>
+      </c>
+      <c r="P52">
+        <f>N52 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>8.9041087156513257E-4</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" ref="Q52:Q90" si="8">G52*O52*91.25</f>
+        <v>0.74649592220075089</v>
+      </c>
+      <c r="R52">
+        <f t="shared" ref="R52:R90" si="9">G52*P52*91.25</f>
+        <v>8.9374991233350194</v>
+      </c>
       <c r="AO52" s="2" t="s">
         <v>55</v>
       </c>
@@ -3479,7 +3646,46 @@
         <v>420</v>
       </c>
     </row>
-    <row r="53" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F53" t="s">
+        <v>56</v>
+      </c>
+      <c r="G53">
+        <v>120</v>
+      </c>
+      <c r="H53">
+        <v>240</v>
+      </c>
+      <c r="I53">
+        <v>0.8</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="6"/>
+        <v>5.6493683855999981</v>
+      </c>
+      <c r="N53">
+        <f>(M53 * (1 -U$11) + (0.04 * M53)) * ( 1 - AD$11 )</f>
+        <v>2.0880065553177594</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="7"/>
+        <v>9.8234527928296858E-5</v>
+      </c>
+      <c r="P53">
+        <f>N53 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.1761229782100196E-3</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="8"/>
+        <v>1.0756680808148507</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="9"/>
+        <v>12.878546611399717</v>
+      </c>
       <c r="AO53" s="2" t="s">
         <v>56</v>
       </c>
@@ -3514,7 +3720,46 @@
         <v>400</v>
       </c>
     </row>
-    <row r="54" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F54" t="s">
+        <v>57</v>
+      </c>
+      <c r="G54">
+        <v>130</v>
+      </c>
+      <c r="H54">
+        <v>280</v>
+      </c>
+      <c r="I54">
+        <v>0.4</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="6"/>
+        <v>5.6565962895999995</v>
+      </c>
+      <c r="N54">
+        <f>(M54 * (1 -V$11) + (0.04 * M54)) * ( 1 - AD$11 )</f>
+        <v>2.5658320769625598</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="7"/>
+        <v>1.2071480435814064E-4</v>
+      </c>
+      <c r="P54">
+        <f>N54 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4452703973837659E-3</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="8"/>
+        <v>1.4319793666984433</v>
+      </c>
+      <c r="R54">
+        <f t="shared" si="9"/>
+        <v>17.144520088964921</v>
+      </c>
       <c r="AO54" s="2" t="s">
         <v>57</v>
       </c>
@@ -3549,7 +3794,48 @@
         <v>400</v>
       </c>
     </row>
-    <row r="55" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="E55" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" t="s">
+        <v>54</v>
+      </c>
+      <c r="H55" cm="1">
+        <f t="array" ref="H55:H58">_xlfn.XLOOKUP(E55, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>480</v>
+      </c>
+      <c r="I55" cm="1">
+        <f t="array" ref="I55:I58">_xlfn.XLOOKUP(E55, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.2</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="6"/>
+        <v>7.9984889855999999</v>
+      </c>
+      <c r="N55">
+        <f>(M55 * (1 -S$11) + (0.04 * M55)) * ( 1 - AD$11 )</f>
+        <v>3.2921780664729599</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="7"/>
+        <v>1.5488723318047602E-4</v>
+      </c>
+      <c r="P55">
+        <f>N55 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.8544033123251509E-3</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM55" t="s">
         <v>69</v>
       </c>
@@ -3587,7 +3873,43 @@
         <v>480</v>
       </c>
     </row>
-    <row r="56" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F56" t="s">
+        <v>55</v>
+      </c>
+      <c r="H56">
+        <v>520</v>
+      </c>
+      <c r="I56">
+        <v>0.4</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="6"/>
+        <v>8.8135359375999975</v>
+      </c>
+      <c r="N56">
+        <f>(M56 * (1 -T$11) + (0.04 * M56)) * ( 1 - AD$11 )</f>
+        <v>2.8873143731577593</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="7"/>
+        <v>1.3583959480652805E-4</v>
+      </c>
+      <c r="P56">
+        <f>N56 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.626353504943911E-3</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO56" s="2" t="s">
         <v>55</v>
       </c>
@@ -3622,7 +3944,43 @@
         <v>460</v>
       </c>
     </row>
-    <row r="57" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F57" t="s">
+        <v>56</v>
+      </c>
+      <c r="H57">
+        <v>550</v>
+      </c>
+      <c r="I57">
+        <v>0.3</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="6"/>
+        <v>8.940100000000001</v>
+      </c>
+      <c r="N57">
+        <f>(M57 * (1 -U$11) + (0.04 * M57)) * ( 1 - AD$11 )</f>
+        <v>3.3042609600000006</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="7"/>
+        <v>1.5545569755555841E-4</v>
+      </c>
+      <c r="P57">
+        <f>N57 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.8612093104596994E-3</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO57" s="2" t="s">
         <v>56</v>
       </c>
@@ -3657,7 +4015,43 @@
         <v>490</v>
       </c>
     </row>
-    <row r="58" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F58" t="s">
+        <v>57</v>
+      </c>
+      <c r="H58">
+        <v>560</v>
+      </c>
+      <c r="I58">
+        <v>0.1</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="6"/>
+        <v>8.6644277315999982</v>
+      </c>
+      <c r="N58">
+        <f>(M58 * (1 -V$11) + (0.04 * M58)) * ( 1 - AD$11 )</f>
+        <v>3.9301844190537589</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="7"/>
+        <v>1.8490354357059897E-4</v>
+      </c>
+      <c r="P58">
+        <f>N58 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.2137766723384039E-3</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO58" s="2" t="s">
         <v>57</v>
       </c>
@@ -3692,7 +4086,48 @@
         <v>470</v>
       </c>
     </row>
-    <row r="59" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="E59" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" t="s">
+        <v>54</v>
+      </c>
+      <c r="H59" cm="1">
+        <f t="array" ref="H59:H62">_xlfn.XLOOKUP(E59, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>75</v>
+      </c>
+      <c r="I59" cm="1">
+        <f t="array" ref="I59:I62">_xlfn.XLOOKUP(E59, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.5</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="6"/>
+        <v>2.7834751406249998</v>
+      </c>
+      <c r="N59">
+        <f>(M59 * (1 -S$11) + (0.04 * M59)) * ( 1 - AD$11 )</f>
+        <v>1.1456783678812499</v>
+      </c>
+      <c r="O59">
+        <f t="shared" si="7"/>
+        <v>5.390077600084388E-5</v>
+      </c>
+      <c r="P59">
+        <f>N59 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>6.4533257842106233E-4</v>
+      </c>
+      <c r="Q59">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM59" t="s">
         <v>70</v>
       </c>
@@ -3730,7 +4165,43 @@
         <v>510</v>
       </c>
     </row>
-    <row r="60" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F60" t="s">
+        <v>55</v>
+      </c>
+      <c r="H60">
+        <v>160</v>
+      </c>
+      <c r="I60">
+        <v>0.9</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="6"/>
+        <v>4.5298311556000002</v>
+      </c>
+      <c r="N60">
+        <f>(M60 * (1 -T$11) + (0.04 * M60)) * ( 1 - AD$11 )</f>
+        <v>1.4839726865745599</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="7"/>
+        <v>6.9816522344180778E-5</v>
+      </c>
+      <c r="P60">
+        <f>N60 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>8.3588548669608228E-4</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO60" s="2" t="s">
         <v>55</v>
       </c>
@@ -3765,7 +4236,43 @@
         <v>520</v>
       </c>
     </row>
-    <row r="61" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F61" t="s">
+        <v>56</v>
+      </c>
+      <c r="H61">
+        <v>220</v>
+      </c>
+      <c r="I61">
+        <v>0.7</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="6"/>
+        <v>5.1913799715999973</v>
+      </c>
+      <c r="N61">
+        <f>(M61 * (1 -U$11) + (0.04 * M61)) * ( 1 - AD$11 )</f>
+        <v>1.918734037503359</v>
+      </c>
+      <c r="O61">
+        <f t="shared" si="7"/>
+        <v>9.0270757011782037E-5</v>
+      </c>
+      <c r="P61">
+        <f>N61 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.0807759127164039E-3</v>
+      </c>
+      <c r="Q61">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO61" s="2" t="s">
         <v>56</v>
       </c>
@@ -3800,7 +4307,43 @@
         <v>410</v>
       </c>
     </row>
-    <row r="62" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F62" t="s">
+        <v>57</v>
+      </c>
+      <c r="H62">
+        <v>260</v>
+      </c>
+      <c r="I62">
+        <v>0.4</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="6"/>
+        <v>5.3621886096000004</v>
+      </c>
+      <c r="N62">
+        <f>(M62 * (1 -V$11) + (0.04 * M62)) * ( 1 - AD$11 )</f>
+        <v>2.4322887533145603</v>
+      </c>
+      <c r="O62">
+        <f t="shared" si="7"/>
+        <v>1.1443198626874025E-4</v>
+      </c>
+      <c r="P62">
+        <f>N62 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.3700487123134107E-3</v>
+      </c>
+      <c r="Q62">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO62" s="2" t="s">
         <v>57</v>
       </c>
@@ -3835,7 +4378,48 @@
         <v>440</v>
       </c>
     </row>
-    <row r="63" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="E63" t="s">
+        <v>45</v>
+      </c>
+      <c r="F63" t="s">
+        <v>54</v>
+      </c>
+      <c r="H63" cm="1">
+        <f t="array" ref="H63:H66">_xlfn.XLOOKUP(E63, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>300</v>
+      </c>
+      <c r="I63" cm="1">
+        <f t="array" ref="I63:I66">_xlfn.XLOOKUP(E63, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="6"/>
+        <v>5.9487209999999981</v>
+      </c>
+      <c r="N63">
+        <f>(M63 * (1 -S$11) + (0.04 * M63)) * ( 1 - AD$11 )</f>
+        <v>2.4484935635999991</v>
+      </c>
+      <c r="O63">
+        <f t="shared" si="7"/>
+        <v>1.1519437462643171E-4</v>
+      </c>
+      <c r="P63">
+        <f>N63 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.3791764852534424E-3</v>
+      </c>
+      <c r="Q63">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM63" t="s">
         <v>65</v>
       </c>
@@ -3876,7 +4460,43 @@
         <v>480</v>
       </c>
     </row>
-    <row r="64" spans="6:51" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F64" t="s">
+        <v>55</v>
+      </c>
+      <c r="H64">
+        <v>360</v>
+      </c>
+      <c r="I64">
+        <v>0.7</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="6"/>
+        <v>7.3058846435999998</v>
+      </c>
+      <c r="N64">
+        <f>(M64 * (1 -T$11) + (0.04 * M64)) * ( 1 - AD$11 )</f>
+        <v>2.3934078092433602</v>
+      </c>
+      <c r="O64">
+        <f t="shared" si="7"/>
+        <v>1.1260275293778476E-4</v>
+      </c>
+      <c r="P64">
+        <f>N64 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.3481480283236143E-3</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO64" s="2" t="s">
         <v>55</v>
       </c>
@@ -3911,7 +4531,43 @@
         <v>470</v>
       </c>
     </row>
-    <row r="65" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="65" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F65" t="s">
+        <v>56</v>
+      </c>
+      <c r="H65">
+        <v>390</v>
+      </c>
+      <c r="I65">
+        <v>0.3</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="6"/>
+        <v>7.0471135296000007</v>
+      </c>
+      <c r="N65">
+        <f>(M65 * (1 -U$11) + (0.04 * M65)) * ( 1 - AD$11 )</f>
+        <v>2.6046131605401603</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="7"/>
+        <v>1.2253933954845938E-4</v>
+      </c>
+      <c r="P65">
+        <f>N65 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4671148324021022E-3</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO65" s="2" t="s">
         <v>56</v>
       </c>
@@ -3946,7 +4602,43 @@
         <v>340</v>
       </c>
     </row>
-    <row r="66" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="66" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F66" t="s">
+        <v>57</v>
+      </c>
+      <c r="H66">
+        <v>410</v>
+      </c>
+      <c r="I66">
+        <v>0.2</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="6"/>
+        <v>7.1414010756000028</v>
+      </c>
+      <c r="N66">
+        <f>(M66 * (1 -V$11) + (0.04 * M66)) * ( 1 - AD$11 )</f>
+        <v>3.2393395278921613</v>
+      </c>
+      <c r="O66">
+        <f t="shared" si="7"/>
+        <v>1.5240133634232363E-4</v>
+      </c>
+      <c r="P66">
+        <f>N66 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.8246406570300113E-3</v>
+      </c>
+      <c r="Q66">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO66" s="2" t="s">
         <v>57</v>
       </c>
@@ -3981,7 +4673,58 @@
         <v>360</v>
       </c>
     </row>
-    <row r="67" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="67" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E67" t="s">
+        <v>46</v>
+      </c>
+      <c r="F67" t="s">
+        <v>54</v>
+      </c>
+      <c r="G67">
+        <v>100</v>
+      </c>
+      <c r="H67" cm="1">
+        <f t="array" ref="H67:H70">_xlfn.XLOOKUP(E67, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>440</v>
+      </c>
+      <c r="I67" cm="1">
+        <f t="array" ref="I67:I70">_xlfn.XLOOKUP(E67, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.3</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>1.3</v>
+      </c>
+      <c r="L67">
+        <f>(J67*K67)+(1 - J67)</f>
+        <v>1.3</v>
+      </c>
+      <c r="M67">
+        <f>(1.185 + 0.00454 * H67 - 0.0000026 * H67^2 + 0.315 * I67)^2 * L67</f>
+        <v>10.001723663880002</v>
+      </c>
+      <c r="N67">
+        <f>(M67 * (1 -S$11) + (0.04 * M67)) * ( 1 - AD$11 )</f>
+        <v>4.1167094600530074</v>
+      </c>
+      <c r="O67">
+        <f t="shared" si="7"/>
+        <v>1.9367899463549227E-4</v>
+      </c>
+      <c r="P67">
+        <f>N67 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.3188416618002772E-3</v>
+      </c>
+      <c r="Q67">
+        <f t="shared" si="8"/>
+        <v>1.7673208260488671</v>
+      </c>
+      <c r="R67">
+        <f t="shared" si="9"/>
+        <v>21.159430163927528</v>
+      </c>
       <c r="AM67" t="s">
         <v>65</v>
       </c>
@@ -4022,7 +4765,53 @@
         <v>370</v>
       </c>
     </row>
-    <row r="68" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="68" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F68" t="s">
+        <v>55</v>
+      </c>
+      <c r="G68">
+        <v>110</v>
+      </c>
+      <c r="H68">
+        <v>470</v>
+      </c>
+      <c r="I68">
+        <v>0.3</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L68">
+        <f t="shared" ref="L68:L74" si="10">(J68*K68)+(1 - J68)</f>
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <f t="shared" ref="M68:M90" si="11">(1.185 + 0.00454 * H68 - 0.0000026 * H68^2 + 0.315 * I68)^2 * L68</f>
+        <v>8.0596938816000012</v>
+      </c>
+      <c r="N68">
+        <f>(M68 * (1 -T$11) + (0.04 * M68)) * ( 1 - AD$11 )</f>
+        <v>2.6403557156121602</v>
+      </c>
+      <c r="O68">
+        <f t="shared" si="7"/>
+        <v>1.2422092096663393E-4</v>
+      </c>
+      <c r="P68">
+        <f>N68 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4872477386964117E-3</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" si="8"/>
+        <v>1.2468674942025881</v>
+      </c>
+      <c r="R68">
+        <f t="shared" si="9"/>
+        <v>14.928249177165233</v>
+      </c>
       <c r="AO68" s="2" t="s">
         <v>55</v>
       </c>
@@ -4057,7 +4846,53 @@
         <v>400</v>
       </c>
     </row>
-    <row r="69" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="69" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F69" t="s">
+        <v>56</v>
+      </c>
+      <c r="G69">
+        <v>120</v>
+      </c>
+      <c r="H69">
+        <v>490</v>
+      </c>
+      <c r="I69">
+        <v>0.2</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="11"/>
+        <v>8.1130407556000002</v>
+      </c>
+      <c r="N69">
+        <f>(M69 * (1 -U$11) + (0.04 * M69)) * ( 1 - AD$11 )</f>
+        <v>2.99857986326976</v>
+      </c>
+      <c r="O69">
+        <f t="shared" si="7"/>
+        <v>1.4107430677044692E-4</v>
+      </c>
+      <c r="P69">
+        <f>N69 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6890266317448027E-3</v>
+      </c>
+      <c r="Q69">
+        <f t="shared" si="8"/>
+        <v>1.5447636591363938</v>
+      </c>
+      <c r="R69">
+        <f t="shared" si="9"/>
+        <v>18.494841617605591</v>
+      </c>
       <c r="AO69" s="2" t="s">
         <v>56</v>
       </c>
@@ -4092,7 +4927,53 @@
         <v>420</v>
       </c>
     </row>
-    <row r="70" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="70" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F70" t="s">
+        <v>57</v>
+      </c>
+      <c r="G70">
+        <v>130</v>
+      </c>
+      <c r="H70">
+        <v>500</v>
+      </c>
+      <c r="I70">
+        <v>0.1</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <f t="shared" si="11"/>
+        <v>8.0457322500000004</v>
+      </c>
+      <c r="N70">
+        <f>(M70 * (1 -V$11) + (0.04 * M70)) * ( 1 - AD$11 )</f>
+        <v>3.6495441486</v>
+      </c>
+      <c r="O70">
+        <f t="shared" si="7"/>
+        <v>1.7170024954095013E-4</v>
+      </c>
+      <c r="P70">
+        <f>N70 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.0556988780656223E-3</v>
+      </c>
+      <c r="Q70">
+        <f t="shared" si="8"/>
+        <v>2.0367942101795209</v>
+      </c>
+      <c r="R70">
+        <f t="shared" si="9"/>
+        <v>24.385727941053442</v>
+      </c>
       <c r="AO70" s="2" t="s">
         <v>57</v>
       </c>
@@ -4127,7 +5008,55 @@
         <v>390</v>
       </c>
     </row>
-    <row r="71" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="71" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E71" t="s">
+        <v>47</v>
+      </c>
+      <c r="F71" t="s">
+        <v>54</v>
+      </c>
+      <c r="H71" cm="1">
+        <f t="array" ref="H71:H74">_xlfn.XLOOKUP(E71, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>440</v>
+      </c>
+      <c r="I71" cm="1">
+        <f t="array" ref="I71:I74">_xlfn.XLOOKUP(E71, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.3</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>1.3</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="10"/>
+        <v>1.3</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="11"/>
+        <v>10.001723663880002</v>
+      </c>
+      <c r="N71">
+        <f>(M71 * (1 -S$11) + (0.04 * M71)) * ( 1 - AD$11 )</f>
+        <v>4.1167094600530074</v>
+      </c>
+      <c r="O71">
+        <f t="shared" si="7"/>
+        <v>1.9367899463549227E-4</v>
+      </c>
+      <c r="P71">
+        <f>N71 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.3188416618002772E-3</v>
+      </c>
+      <c r="Q71">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM71" t="s">
         <v>65</v>
       </c>
@@ -4168,7 +5097,50 @@
         <v>340</v>
       </c>
     </row>
-    <row r="72" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="72" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F72" t="s">
+        <v>55</v>
+      </c>
+      <c r="H72">
+        <v>470</v>
+      </c>
+      <c r="I72">
+        <v>0.3</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="11"/>
+        <v>8.0596938816000012</v>
+      </c>
+      <c r="N72">
+        <f>(M72 * (1 -T$11) + (0.04 * M72)) * ( 1 - AD$11 )</f>
+        <v>2.6403557156121602</v>
+      </c>
+      <c r="O72">
+        <f t="shared" si="7"/>
+        <v>1.2422092096663393E-4</v>
+      </c>
+      <c r="P72">
+        <f>N72 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4872477386964117E-3</v>
+      </c>
+      <c r="Q72">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO72" s="2" t="s">
         <v>55</v>
       </c>
@@ -4203,7 +5175,50 @@
         <v>390</v>
       </c>
     </row>
-    <row r="73" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="73" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F73" t="s">
+        <v>56</v>
+      </c>
+      <c r="H73">
+        <v>490</v>
+      </c>
+      <c r="I73">
+        <v>0.2</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="11"/>
+        <v>8.1130407556000002</v>
+      </c>
+      <c r="N73">
+        <f>(M73 * (1 -U$11) + (0.04 * M73)) * ( 1 - AD$11 )</f>
+        <v>2.99857986326976</v>
+      </c>
+      <c r="O73">
+        <f t="shared" si="7"/>
+        <v>1.4107430677044692E-4</v>
+      </c>
+      <c r="P73">
+        <f>N73 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6890266317448027E-3</v>
+      </c>
+      <c r="Q73">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO73" s="2" t="s">
         <v>56</v>
       </c>
@@ -4238,7 +5253,50 @@
         <v>430</v>
       </c>
     </row>
-    <row r="74" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="74" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H74">
+        <v>500</v>
+      </c>
+      <c r="I74">
+        <v>0.1</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+      <c r="L74">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <f t="shared" si="11"/>
+        <v>8.0457322500000004</v>
+      </c>
+      <c r="N74">
+        <f>(M74 * (1 -V$11) + (0.04 * M74)) * ( 1 - AD$11 )</f>
+        <v>3.6495441486</v>
+      </c>
+      <c r="O74">
+        <f t="shared" si="7"/>
+        <v>1.7170024954095013E-4</v>
+      </c>
+      <c r="P74">
+        <f>N74 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.0556988780656223E-3</v>
+      </c>
+      <c r="Q74">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO74" s="2" t="s">
         <v>57</v>
       </c>
@@ -4273,7 +5331,51 @@
         <v>400</v>
       </c>
     </row>
-    <row r="75" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="75" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E75" t="s">
+        <v>48</v>
+      </c>
+      <c r="F75" t="s">
+        <v>54</v>
+      </c>
+      <c r="G75">
+        <v>200</v>
+      </c>
+      <c r="H75" cm="1">
+        <f t="array" ref="H75:H78">_xlfn.XLOOKUP(E75, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>75</v>
+      </c>
+      <c r="I75" cm="1">
+        <f t="array" ref="I75:I78">_xlfn.XLOOKUP(E75, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.5</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <f t="shared" si="11"/>
+        <v>2.7834751406249998</v>
+      </c>
+      <c r="N75">
+        <f>(M75 * (1 -S$11) + (0.04 * M75)) * ( 1 - AD$11 )</f>
+        <v>1.1456783678812499</v>
+      </c>
+      <c r="O75">
+        <f t="shared" si="7"/>
+        <v>5.390077600084388E-5</v>
+      </c>
+      <c r="P75">
+        <f>N75 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>6.4533257842106233E-4</v>
+      </c>
+      <c r="Q75">
+        <f t="shared" si="8"/>
+        <v>0.98368916201540069</v>
+      </c>
+      <c r="R75">
+        <f t="shared" si="9"/>
+        <v>11.777319556184386</v>
+      </c>
       <c r="AM75" t="s">
         <v>73</v>
       </c>
@@ -4314,7 +5416,46 @@
         <v>585</v>
       </c>
     </row>
-    <row r="76" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="76" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F76" t="s">
+        <v>55</v>
+      </c>
+      <c r="G76">
+        <v>130</v>
+      </c>
+      <c r="H76">
+        <v>160</v>
+      </c>
+      <c r="I76">
+        <v>0.9</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <f t="shared" si="11"/>
+        <v>4.5298311556000002</v>
+      </c>
+      <c r="N76">
+        <f>(M76 * (1 -T$11) + (0.04 * M76)) * ( 1 - AD$11 )</f>
+        <v>1.4839726865745599</v>
+      </c>
+      <c r="O76">
+        <f t="shared" si="7"/>
+        <v>6.9816522344180778E-5</v>
+      </c>
+      <c r="P76">
+        <f>N76 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>8.3588548669608228E-4</v>
+      </c>
+      <c r="Q76">
+        <f t="shared" si="8"/>
+        <v>0.82819849630784437</v>
+      </c>
+      <c r="R76">
+        <f t="shared" si="9"/>
+        <v>9.9156915859322758</v>
+      </c>
       <c r="AO76" s="2" t="s">
         <v>55</v>
       </c>
@@ -4349,7 +5490,46 @@
         <v>543</v>
       </c>
     </row>
-    <row r="77" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="77" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F77" t="s">
+        <v>56</v>
+      </c>
+      <c r="G77">
+        <v>250</v>
+      </c>
+      <c r="H77">
+        <v>220</v>
+      </c>
+      <c r="I77">
+        <v>0.7</v>
+      </c>
+      <c r="L77">
+        <v>1</v>
+      </c>
+      <c r="M77">
+        <f t="shared" si="11"/>
+        <v>5.1913799715999973</v>
+      </c>
+      <c r="N77">
+        <f>(M77 * (1 -U$11) + (0.04 * M77)) * ( 1 - AD$11 )</f>
+        <v>1.918734037503359</v>
+      </c>
+      <c r="O77">
+        <f t="shared" si="7"/>
+        <v>9.0270757011782037E-5</v>
+      </c>
+      <c r="P77">
+        <f>N77 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.0807759127164039E-3</v>
+      </c>
+      <c r="Q77">
+        <f t="shared" si="8"/>
+        <v>2.0593016443312777</v>
+      </c>
+      <c r="R77">
+        <f t="shared" si="9"/>
+        <v>24.655200508842963</v>
+      </c>
       <c r="AO77" s="2" t="s">
         <v>56</v>
       </c>
@@ -4384,7 +5564,46 @@
         <v>580</v>
       </c>
     </row>
-    <row r="78" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="78" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F78" t="s">
+        <v>57</v>
+      </c>
+      <c r="G78">
+        <v>150</v>
+      </c>
+      <c r="H78">
+        <v>260</v>
+      </c>
+      <c r="I78">
+        <v>0.4</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <f t="shared" si="11"/>
+        <v>5.3621886096000004</v>
+      </c>
+      <c r="N78">
+        <f>(M78 * (1 -V$11) + (0.04 * M78)) * ( 1 - AD$11 )</f>
+        <v>2.4322887533145603</v>
+      </c>
+      <c r="O78">
+        <f t="shared" si="7"/>
+        <v>1.1443198626874025E-4</v>
+      </c>
+      <c r="P78">
+        <f>N78 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.3700487123134107E-3</v>
+      </c>
+      <c r="Q78">
+        <f t="shared" si="8"/>
+        <v>1.5662878120533821</v>
+      </c>
+      <c r="R78">
+        <f t="shared" si="9"/>
+        <v>18.75254174978981</v>
+      </c>
       <c r="AO78" s="2" t="s">
         <v>57</v>
       </c>
@@ -4419,7 +5638,48 @@
         <v>590</v>
       </c>
     </row>
-    <row r="79" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="79" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E79" t="s">
+        <v>49</v>
+      </c>
+      <c r="F79" t="s">
+        <v>54</v>
+      </c>
+      <c r="H79" cm="1">
+        <f t="array" ref="H79:H82">_xlfn.XLOOKUP(E79, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>380</v>
+      </c>
+      <c r="I79" cm="1">
+        <f t="array" ref="I79:I82">_xlfn.XLOOKUP(E79, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <f t="shared" si="11"/>
+        <v>7.0796437775999967</v>
+      </c>
+      <c r="N79">
+        <f>(M79 * (1 -S$11) + (0.04 * M79)) * ( 1 - AD$11 )</f>
+        <v>2.9139813788601581</v>
+      </c>
+      <c r="O79">
+        <f t="shared" si="7"/>
+        <v>1.37094198490489E-4</v>
+      </c>
+      <c r="P79">
+        <f>N79 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6413743764477724E-3</v>
+      </c>
+      <c r="Q79">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM79" t="s">
         <v>73</v>
       </c>
@@ -4460,7 +5720,43 @@
         <v>72</v>
       </c>
     </row>
-    <row r="80" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="80" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F80" t="s">
+        <v>55</v>
+      </c>
+      <c r="H80">
+        <v>420</v>
+      </c>
+      <c r="I80">
+        <v>0.4</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="M80">
+        <f t="shared" si="11"/>
+        <v>7.6129639056</v>
+      </c>
+      <c r="N80">
+        <f>(M80 * (1 -T$11) + (0.04 * M80)) * ( 1 - AD$11 )</f>
+        <v>2.49400697547456</v>
+      </c>
+      <c r="O80">
+        <f t="shared" si="7"/>
+        <v>1.1733564593543065E-4</v>
+      </c>
+      <c r="P80">
+        <f>N80 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4048130759940598E-3</v>
+      </c>
+      <c r="Q80">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO80" s="2" t="s">
         <v>55</v>
       </c>
@@ -4495,7 +5791,43 @@
         <v>72</v>
       </c>
     </row>
-    <row r="81" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F81" t="s">
+        <v>56</v>
+      </c>
+      <c r="H81">
+        <v>450</v>
+      </c>
+      <c r="I81">
+        <v>0.3</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <f t="shared" si="11"/>
+        <v>7.8176159999999992</v>
+      </c>
+      <c r="N81">
+        <f>(M81 * (1 -U$11) + (0.04 * M81)) * ( 1 - AD$11 )</f>
+        <v>2.8893908736</v>
+      </c>
+      <c r="O81">
+        <f t="shared" si="7"/>
+        <v>1.3593728800589413E-4</v>
+      </c>
+      <c r="P81">
+        <f>N81 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.627523146810294E-3</v>
+      </c>
+      <c r="Q81">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO81" s="2" t="s">
         <v>56</v>
       </c>
@@ -4530,7 +5862,43 @@
         <v>72</v>
       </c>
     </row>
-    <row r="82" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F82" t="s">
+        <v>57</v>
+      </c>
+      <c r="H82">
+        <v>460</v>
+      </c>
+      <c r="I82">
+        <v>0.1</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <f t="shared" si="11"/>
+        <v>7.5885924675999998</v>
+      </c>
+      <c r="N82">
+        <f>(M82 * (1 -V$11) + (0.04 * M82)) * ( 1 - AD$11 )</f>
+        <v>3.4421855433033599</v>
+      </c>
+      <c r="O82">
+        <f t="shared" si="7"/>
+        <v>1.6194464094321492E-4</v>
+      </c>
+      <c r="P82">
+        <f>N82 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.9388988518406825E-3</v>
+      </c>
+      <c r="Q82">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO82" s="2" t="s">
         <v>57</v>
       </c>
@@ -4565,7 +5933,48 @@
         <v>72</v>
       </c>
     </row>
-    <row r="83" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="E83" t="s">
+        <v>50</v>
+      </c>
+      <c r="F83" t="s">
+        <v>54</v>
+      </c>
+      <c r="H83" cm="1">
+        <f t="array" ref="H83:H86">_xlfn.XLOOKUP(E83, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>380</v>
+      </c>
+      <c r="I83" cm="1">
+        <f t="array" ref="I83:I86">_xlfn.XLOOKUP(E83, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <f t="shared" si="11"/>
+        <v>7.0796437775999967</v>
+      </c>
+      <c r="N83">
+        <f>(M83 * (1 -S$11) + (0.04 * M83)) * ( 1 - AD$11 )</f>
+        <v>2.9139813788601581</v>
+      </c>
+      <c r="O83">
+        <f t="shared" si="7"/>
+        <v>1.37094198490489E-4</v>
+      </c>
+      <c r="P83">
+        <f>N83 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6413743764477724E-3</v>
+      </c>
+      <c r="Q83">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM83" t="s">
         <v>73</v>
       </c>
@@ -4606,7 +6015,43 @@
         <v>72</v>
       </c>
     </row>
-    <row r="84" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F84" t="s">
+        <v>55</v>
+      </c>
+      <c r="H84">
+        <v>420</v>
+      </c>
+      <c r="I84">
+        <v>0.4</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <f t="shared" si="11"/>
+        <v>7.6129639056</v>
+      </c>
+      <c r="N84">
+        <f>(M84 * (1 -T$11) + (0.04 * M84)) * ( 1 - AD$11 )</f>
+        <v>2.49400697547456</v>
+      </c>
+      <c r="O84">
+        <f t="shared" si="7"/>
+        <v>1.1733564593543065E-4</v>
+      </c>
+      <c r="P84">
+        <f>N84 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4048130759940598E-3</v>
+      </c>
+      <c r="Q84">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO84" s="2" t="s">
         <v>55</v>
       </c>
@@ -4641,7 +6086,43 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F85" t="s">
+        <v>56</v>
+      </c>
+      <c r="H85">
+        <v>450</v>
+      </c>
+      <c r="I85">
+        <v>0.3</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <f t="shared" si="11"/>
+        <v>7.8176159999999992</v>
+      </c>
+      <c r="N85">
+        <f>(M85 * (1 -U$11) + (0.04 * M85)) * ( 1 - AD$11 )</f>
+        <v>2.8893908736</v>
+      </c>
+      <c r="O85">
+        <f t="shared" si="7"/>
+        <v>1.3593728800589413E-4</v>
+      </c>
+      <c r="P85">
+        <f>N85 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.627523146810294E-3</v>
+      </c>
+      <c r="Q85">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO85" s="2" t="s">
         <v>56</v>
       </c>
@@ -4676,7 +6157,43 @@
         <v>72</v>
       </c>
     </row>
-    <row r="86" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F86" t="s">
+        <v>57</v>
+      </c>
+      <c r="H86">
+        <v>460</v>
+      </c>
+      <c r="I86">
+        <v>0.1</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <f t="shared" si="11"/>
+        <v>7.5885924675999998</v>
+      </c>
+      <c r="N86">
+        <f>(M86 * (1 -V$11) + (0.04 * M86)) * ( 1 - AD$11 )</f>
+        <v>3.4421855433033599</v>
+      </c>
+      <c r="O86">
+        <f t="shared" si="7"/>
+        <v>1.6194464094321492E-4</v>
+      </c>
+      <c r="P86">
+        <f>N86 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.9388988518406825E-3</v>
+      </c>
+      <c r="Q86">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO86" s="2" t="s">
         <v>57</v>
       </c>
@@ -4711,7 +6228,48 @@
         <v>72</v>
       </c>
     </row>
-    <row r="87" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="E87" t="s">
+        <v>51</v>
+      </c>
+      <c r="F87" t="s">
+        <v>54</v>
+      </c>
+      <c r="H87" cm="1">
+        <f t="array" ref="H87:H90">_xlfn.XLOOKUP(E87, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>380</v>
+      </c>
+      <c r="I87" cm="1">
+        <f t="array" ref="I87:I90">_xlfn.XLOOKUP(E87, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="11"/>
+        <v>7.0796437775999967</v>
+      </c>
+      <c r="N87">
+        <f>(M87 * (1 -S$11) + (0.04 * M87)) * ( 1 - AD$11 )</f>
+        <v>2.9139813788601581</v>
+      </c>
+      <c r="O87">
+        <f t="shared" si="7"/>
+        <v>1.37094198490489E-4</v>
+      </c>
+      <c r="P87">
+        <f>N87 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6413743764477724E-3</v>
+      </c>
+      <c r="Q87">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AM87" t="s">
         <v>81</v>
       </c>
@@ -4752,7 +6310,43 @@
         <v>660</v>
       </c>
     </row>
-    <row r="88" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F88" t="s">
+        <v>55</v>
+      </c>
+      <c r="H88">
+        <v>420</v>
+      </c>
+      <c r="I88">
+        <v>0.4</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <f t="shared" si="11"/>
+        <v>7.6129639056</v>
+      </c>
+      <c r="N88">
+        <f>(M88 * (1 -T$11) + (0.04 * M88)) * ( 1 - AD$11 )</f>
+        <v>2.49400697547456</v>
+      </c>
+      <c r="O88">
+        <f t="shared" si="7"/>
+        <v>1.1733564593543065E-4</v>
+      </c>
+      <c r="P88">
+        <f>N88 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4048130759940598E-3</v>
+      </c>
+      <c r="Q88">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO88" s="2" t="s">
         <v>55</v>
       </c>
@@ -4787,7 +6381,43 @@
         <v>547</v>
       </c>
     </row>
-    <row r="89" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F89" t="s">
+        <v>56</v>
+      </c>
+      <c r="H89">
+        <v>450</v>
+      </c>
+      <c r="I89">
+        <v>0.3</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89">
+        <f t="shared" si="11"/>
+        <v>7.8176159999999992</v>
+      </c>
+      <c r="N89">
+        <f>(M89 * (1 -U$11) + (0.04 * M89)) * ( 1 - AD$11 )</f>
+        <v>2.8893908736</v>
+      </c>
+      <c r="O89">
+        <f t="shared" si="7"/>
+        <v>1.3593728800589413E-4</v>
+      </c>
+      <c r="P89">
+        <f>N89 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.627523146810294E-3</v>
+      </c>
+      <c r="Q89">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO89" s="2" t="s">
         <v>56</v>
       </c>
@@ -4822,7 +6452,43 @@
         <v>582</v>
       </c>
     </row>
-    <row r="90" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F90" t="s">
+        <v>57</v>
+      </c>
+      <c r="H90">
+        <v>460</v>
+      </c>
+      <c r="I90">
+        <v>0.1</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <f t="shared" si="11"/>
+        <v>7.5885924675999998</v>
+      </c>
+      <c r="N90">
+        <f>(M90 * (1 -V$11) + (0.04 * M90)) * ( 1 - AD$11 )</f>
+        <v>3.4421855433033599</v>
+      </c>
+      <c r="O90">
+        <f t="shared" si="7"/>
+        <v>1.6194464094321492E-4</v>
+      </c>
+      <c r="P90">
+        <f>N90 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.9388988518406825E-3</v>
+      </c>
+      <c r="Q90">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AO90" s="2" t="s">
         <v>57</v>
       </c>
@@ -4857,7 +6523,122 @@
         <v>605</v>
       </c>
     </row>
-    <row r="91" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>118</v>
+      </c>
+      <c r="B91" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" t="s">
+        <v>53</v>
+      </c>
+      <c r="D91" t="s">
+        <v>53</v>
+      </c>
+      <c r="E91" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" t="s">
+        <v>54</v>
+      </c>
+      <c r="G91">
+        <v>100</v>
+      </c>
+      <c r="H91" cm="1">
+        <f t="array" ref="H91:H94">_xlfn.XLOOKUP(E91, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>80</v>
+      </c>
+      <c r="I91" cm="1">
+        <f t="array" ref="I91:I94">_xlfn.XLOOKUP(E91, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.5</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <f>(1.185 + 0.00454 * H91 - 0.0000026 * H91^2 + 0.315 * I91)^2 * L91</f>
+        <v>2.8529236835999998</v>
+      </c>
+      <c r="N91">
+        <f>(M91 * (1 -S91) + (0.04 * M91)) * ( 1 - AD$11 )</f>
+        <v>1.1742633881697597</v>
+      </c>
+      <c r="O91">
+        <f>N91 * AB$51 * X$51 * Z$51 * AC$51</f>
+        <v>5.5245616593758213E-5</v>
+      </c>
+      <c r="P91">
+        <f>N91 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>6.6143382058828331E-4</v>
+      </c>
+      <c r="Q91">
+        <f>G91*O91*91.25</f>
+        <v>0.50411625141804373</v>
+      </c>
+      <c r="R91">
+        <f>G91*P91*91.25</f>
+        <v>6.0355836128680851</v>
+      </c>
+      <c r="S91" cm="1">
+        <f t="array" ref="S91:V91">_xlfn.XLOOKUP(C91,$AR$18:$AR$26,$AS$18:$AV$26)</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T91">
+        <v>0.65</v>
+      </c>
+      <c r="U91">
+        <v>0.6</v>
+      </c>
+      <c r="V91">
+        <v>0.5</v>
+      </c>
+      <c r="W91" t="s">
+        <v>91</v>
+      </c>
+      <c r="X91">
+        <f>IF(W91="yes", $AN$6, $AO$6)</f>
+        <v>0.05</v>
+      </c>
+      <c r="Y91">
+        <f>IF(W91="yes", $AN$7, $AO$7)</f>
+        <v>0.95</v>
+      </c>
+      <c r="Z91">
+        <f>VLOOKUP(B91, $AZ$17:$BA$26, 2, FALSE)</f>
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="AA91">
+        <f>$BA$14</f>
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="AB91">
+        <f>$AS$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="AC91">
+        <f>$AS$6</f>
+        <v>0.6784</v>
+      </c>
+      <c r="AD91">
+        <f>$AS$7</f>
+        <v>0.16</v>
+      </c>
+      <c r="AE91">
+        <f>SUM(Q91:R130)</f>
+        <v>204.8566346624763</v>
+      </c>
+      <c r="AF91">
+        <f>$AS$8</f>
+        <v>28</v>
+      </c>
+      <c r="AG91">
+        <f>AE91 * AF91 * 10^-3</f>
+        <v>5.7359857705493358</v>
+      </c>
       <c r="AM91" t="s">
         <v>81</v>
       </c>
@@ -4898,7 +6679,46 @@
         <v>620</v>
       </c>
     </row>
-    <row r="92" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F92" t="s">
+        <v>55</v>
+      </c>
+      <c r="G92">
+        <v>110</v>
+      </c>
+      <c r="H92">
+        <v>170</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
+        <f t="shared" ref="M92:M106" si="12">(1.185 + 0.00454 * H92 - 0.0000026 * H92^2 + 0.315 * I92)^2 * L92</f>
+        <v>4.8253151556000002</v>
+      </c>
+      <c r="N92">
+        <f>(M92 * (1 -T$11) + (0.04 * M92)) * ( 1 - AD$11 )</f>
+        <v>1.58077324497456</v>
+      </c>
+      <c r="O92">
+        <f t="shared" ref="O92:O130" si="13">N92 * AB$51 * X$51 * Z$51 * AC$51</f>
+        <v>7.4370702087247912E-5</v>
+      </c>
+      <c r="P92">
+        <f>N92 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>8.9041087156513257E-4</v>
+      </c>
+      <c r="Q92">
+        <f t="shared" ref="Q92:Q130" si="14">G92*O92*91.25</f>
+        <v>0.74649592220075089</v>
+      </c>
+      <c r="R92">
+        <f t="shared" ref="R92:R130" si="15">G92*P92*91.25</f>
+        <v>8.9374991233350194</v>
+      </c>
       <c r="AO92" s="2" t="s">
         <v>55</v>
       </c>
@@ -4933,7 +6753,46 @@
         <v>553</v>
       </c>
     </row>
-    <row r="93" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F93" t="s">
+        <v>56</v>
+      </c>
+      <c r="G93">
+        <v>120</v>
+      </c>
+      <c r="H93">
+        <v>240</v>
+      </c>
+      <c r="I93">
+        <v>0.8</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93">
+        <f t="shared" si="12"/>
+        <v>5.6493683855999981</v>
+      </c>
+      <c r="N93">
+        <f>(M93 * (1 -U$11) + (0.04 * M93)) * ( 1 - AD$11 )</f>
+        <v>2.0880065553177594</v>
+      </c>
+      <c r="O93">
+        <f t="shared" si="13"/>
+        <v>9.8234527928296858E-5</v>
+      </c>
+      <c r="P93">
+        <f>N93 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.1761229782100196E-3</v>
+      </c>
+      <c r="Q93">
+        <f t="shared" si="14"/>
+        <v>1.0756680808148507</v>
+      </c>
+      <c r="R93">
+        <f t="shared" si="15"/>
+        <v>12.878546611399717</v>
+      </c>
       <c r="AO93" s="2" t="s">
         <v>56</v>
       </c>
@@ -4968,7 +6827,46 @@
         <v>620</v>
       </c>
     </row>
-    <row r="94" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F94" t="s">
+        <v>57</v>
+      </c>
+      <c r="G94">
+        <v>130</v>
+      </c>
+      <c r="H94">
+        <v>280</v>
+      </c>
+      <c r="I94">
+        <v>0.4</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94">
+        <f t="shared" si="12"/>
+        <v>5.6565962895999995</v>
+      </c>
+      <c r="N94">
+        <f>(M94 * (1 -V$11) + (0.04 * M94)) * ( 1 - AD$11 )</f>
+        <v>2.5658320769625598</v>
+      </c>
+      <c r="O94">
+        <f t="shared" si="13"/>
+        <v>1.2071480435814064E-4</v>
+      </c>
+      <c r="P94">
+        <f>N94 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4452703973837659E-3</v>
+      </c>
+      <c r="Q94">
+        <f t="shared" si="14"/>
+        <v>1.4319793666984433</v>
+      </c>
+      <c r="R94">
+        <f t="shared" si="15"/>
+        <v>17.144520088964921</v>
+      </c>
       <c r="AO94" s="2" t="s">
         <v>57</v>
       </c>
@@ -5003,7 +6901,48 @@
         <v>620</v>
       </c>
     </row>
-    <row r="95" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="E95" t="s">
+        <v>43</v>
+      </c>
+      <c r="F95" t="s">
+        <v>54</v>
+      </c>
+      <c r="H95" cm="1">
+        <f t="array" ref="H95:H98">_xlfn.XLOOKUP(E95, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>480</v>
+      </c>
+      <c r="I95" cm="1">
+        <f t="array" ref="I95:I98">_xlfn.XLOOKUP(E95, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.2</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <f t="shared" si="12"/>
+        <v>7.9984889855999999</v>
+      </c>
+      <c r="N95">
+        <f>(M95 * (1 -S$11) + (0.04 * M95)) * ( 1 - AD$11 )</f>
+        <v>3.2921780664729599</v>
+      </c>
+      <c r="O95">
+        <f t="shared" si="13"/>
+        <v>1.5488723318047602E-4</v>
+      </c>
+      <c r="P95">
+        <f>N95 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.8544033123251509E-3</v>
+      </c>
+      <c r="Q95">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R95">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AM95" t="s">
         <v>81</v>
       </c>
@@ -5044,7 +6983,43 @@
         <v>565</v>
       </c>
     </row>
-    <row r="96" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F96" t="s">
+        <v>55</v>
+      </c>
+      <c r="H96">
+        <v>520</v>
+      </c>
+      <c r="I96">
+        <v>0.4</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <f t="shared" si="12"/>
+        <v>8.8135359375999975</v>
+      </c>
+      <c r="N96">
+        <f>(M96 * (1 -T$11) + (0.04 * M96)) * ( 1 - AD$11 )</f>
+        <v>2.8873143731577593</v>
+      </c>
+      <c r="O96">
+        <f t="shared" si="13"/>
+        <v>1.3583959480652805E-4</v>
+      </c>
+      <c r="P96">
+        <f>N96 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.626353504943911E-3</v>
+      </c>
+      <c r="Q96">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R96">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO96" s="2" t="s">
         <v>55</v>
       </c>
@@ -5079,7 +7054,43 @@
         <v>556</v>
       </c>
     </row>
-    <row r="97" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="97" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F97" t="s">
+        <v>56</v>
+      </c>
+      <c r="H97">
+        <v>550</v>
+      </c>
+      <c r="I97">
+        <v>0.3</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <f t="shared" si="12"/>
+        <v>8.940100000000001</v>
+      </c>
+      <c r="N97">
+        <f>(M97 * (1 -U$11) + (0.04 * M97)) * ( 1 - AD$11 )</f>
+        <v>3.3042609600000006</v>
+      </c>
+      <c r="O97">
+        <f t="shared" si="13"/>
+        <v>1.5545569755555841E-4</v>
+      </c>
+      <c r="P97">
+        <f>N97 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.8612093104596994E-3</v>
+      </c>
+      <c r="Q97">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R97">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO97" s="2" t="s">
         <v>56</v>
       </c>
@@ -5114,7 +7125,43 @@
         <v>593</v>
       </c>
     </row>
-    <row r="98" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="98" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F98" t="s">
+        <v>57</v>
+      </c>
+      <c r="H98">
+        <v>560</v>
+      </c>
+      <c r="I98">
+        <v>0.1</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <f t="shared" si="12"/>
+        <v>8.6644277315999982</v>
+      </c>
+      <c r="N98">
+        <f>(M98 * (1 -V$11) + (0.04 * M98)) * ( 1 - AD$11 )</f>
+        <v>3.9301844190537589</v>
+      </c>
+      <c r="O98">
+        <f t="shared" si="13"/>
+        <v>1.8490354357059897E-4</v>
+      </c>
+      <c r="P98">
+        <f>N98 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.2137766723384039E-3</v>
+      </c>
+      <c r="Q98">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R98">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO98" s="2" t="s">
         <v>57</v>
       </c>
@@ -5149,7 +7196,48 @@
         <v>553</v>
       </c>
     </row>
-    <row r="99" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="99" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E99" t="s">
+        <v>44</v>
+      </c>
+      <c r="F99" t="s">
+        <v>54</v>
+      </c>
+      <c r="H99" cm="1">
+        <f t="array" ref="H99:H102">_xlfn.XLOOKUP(E99, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>75</v>
+      </c>
+      <c r="I99" cm="1">
+        <f t="array" ref="I99:I102">_xlfn.XLOOKUP(E99, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.5</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <f t="shared" si="12"/>
+        <v>2.7834751406249998</v>
+      </c>
+      <c r="N99">
+        <f>(M99 * (1 -S$11) + (0.04 * M99)) * ( 1 - AD$11 )</f>
+        <v>1.1456783678812499</v>
+      </c>
+      <c r="O99">
+        <f t="shared" si="13"/>
+        <v>5.390077600084388E-5</v>
+      </c>
+      <c r="P99">
+        <f>N99 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>6.4533257842106233E-4</v>
+      </c>
+      <c r="Q99">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R99">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AM99" t="s">
         <v>81</v>
       </c>
@@ -5190,7 +7278,43 @@
         <v>531</v>
       </c>
     </row>
-    <row r="100" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="100" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H100">
+        <v>160</v>
+      </c>
+      <c r="I100">
+        <v>0.9</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <f t="shared" si="12"/>
+        <v>4.5298311556000002</v>
+      </c>
+      <c r="N100">
+        <f>(M100 * (1 -T$11) + (0.04 * M100)) * ( 1 - AD$11 )</f>
+        <v>1.4839726865745599</v>
+      </c>
+      <c r="O100">
+        <f t="shared" si="13"/>
+        <v>6.9816522344180778E-5</v>
+      </c>
+      <c r="P100">
+        <f>N100 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>8.3588548669608228E-4</v>
+      </c>
+      <c r="Q100">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R100">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO100" s="2" t="s">
         <v>55</v>
       </c>
@@ -5225,7 +7349,43 @@
         <v>445</v>
       </c>
     </row>
-    <row r="101" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="101" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F101" t="s">
+        <v>56</v>
+      </c>
+      <c r="H101">
+        <v>220</v>
+      </c>
+      <c r="I101">
+        <v>0.7</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="M101">
+        <f t="shared" si="12"/>
+        <v>5.1913799715999973</v>
+      </c>
+      <c r="N101">
+        <f>(M101 * (1 -U$11) + (0.04 * M101)) * ( 1 - AD$11 )</f>
+        <v>1.918734037503359</v>
+      </c>
+      <c r="O101">
+        <f t="shared" si="13"/>
+        <v>9.0270757011782037E-5</v>
+      </c>
+      <c r="P101">
+        <f>N101 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.0807759127164039E-3</v>
+      </c>
+      <c r="Q101">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R101">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO101" s="2" t="s">
         <v>56</v>
       </c>
@@ -5260,7 +7420,43 @@
         <v>471</v>
       </c>
     </row>
-    <row r="102" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="102" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F102" t="s">
+        <v>57</v>
+      </c>
+      <c r="H102">
+        <v>260</v>
+      </c>
+      <c r="I102">
+        <v>0.4</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102">
+        <f t="shared" si="12"/>
+        <v>5.3621886096000004</v>
+      </c>
+      <c r="N102">
+        <f>(M102 * (1 -V$11) + (0.04 * M102)) * ( 1 - AD$11 )</f>
+        <v>2.4322887533145603</v>
+      </c>
+      <c r="O102">
+        <f t="shared" si="13"/>
+        <v>1.1443198626874025E-4</v>
+      </c>
+      <c r="P102">
+        <f>N102 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.3700487123134107E-3</v>
+      </c>
+      <c r="Q102">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R102">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO102" s="2" t="s">
         <v>57</v>
       </c>
@@ -5295,7 +7491,162 @@
         <v>484</v>
       </c>
     </row>
-    <row r="106" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="103" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E103" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103" t="s">
+        <v>54</v>
+      </c>
+      <c r="H103" cm="1">
+        <f t="array" ref="H103:H106">_xlfn.XLOOKUP(E103, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>300</v>
+      </c>
+      <c r="I103" cm="1">
+        <f t="array" ref="I103:I106">_xlfn.XLOOKUP(E103, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103">
+        <f t="shared" si="12"/>
+        <v>5.9487209999999981</v>
+      </c>
+      <c r="N103">
+        <f>(M103 * (1 -S$11) + (0.04 * M103)) * ( 1 - AD$11 )</f>
+        <v>2.4484935635999991</v>
+      </c>
+      <c r="O103">
+        <f t="shared" si="13"/>
+        <v>1.1519437462643171E-4</v>
+      </c>
+      <c r="P103">
+        <f>N103 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.3791764852534424E-3</v>
+      </c>
+      <c r="Q103">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R103">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F104" t="s">
+        <v>55</v>
+      </c>
+      <c r="H104">
+        <v>360</v>
+      </c>
+      <c r="I104">
+        <v>0.7</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104">
+        <f t="shared" si="12"/>
+        <v>7.3058846435999998</v>
+      </c>
+      <c r="N104">
+        <f>(M104 * (1 -T$11) + (0.04 * M104)) * ( 1 - AD$11 )</f>
+        <v>2.3934078092433602</v>
+      </c>
+      <c r="O104">
+        <f t="shared" si="13"/>
+        <v>1.1260275293778476E-4</v>
+      </c>
+      <c r="P104">
+        <f>N104 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.3481480283236143E-3</v>
+      </c>
+      <c r="Q104">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R104">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F105" t="s">
+        <v>56</v>
+      </c>
+      <c r="H105">
+        <v>390</v>
+      </c>
+      <c r="I105">
+        <v>0.3</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <f t="shared" si="12"/>
+        <v>7.0471135296000007</v>
+      </c>
+      <c r="N105">
+        <f>(M105 * (1 -U$11) + (0.04 * M105)) * ( 1 - AD$11 )</f>
+        <v>2.6046131605401603</v>
+      </c>
+      <c r="O105">
+        <f t="shared" si="13"/>
+        <v>1.2253933954845938E-4</v>
+      </c>
+      <c r="P105">
+        <f>N105 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4671148324021022E-3</v>
+      </c>
+      <c r="Q105">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R105">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F106" t="s">
+        <v>57</v>
+      </c>
+      <c r="H106">
+        <v>410</v>
+      </c>
+      <c r="I106">
+        <v>0.2</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <f t="shared" si="12"/>
+        <v>7.1414010756000028</v>
+      </c>
+      <c r="N106">
+        <f>(M106 * (1 -V$11) + (0.04 * M106)) * ( 1 - AD$11 )</f>
+        <v>3.2393395278921613</v>
+      </c>
+      <c r="O106">
+        <f t="shared" si="13"/>
+        <v>1.5240133634232363E-4</v>
+      </c>
+      <c r="P106">
+        <f>N106 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.8246406570300113E-3</v>
+      </c>
+      <c r="Q106">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R106">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AM106" t="s">
         <v>60</v>
       </c>
@@ -5330,7 +7681,58 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="107" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E107" t="s">
+        <v>46</v>
+      </c>
+      <c r="F107" t="s">
+        <v>54</v>
+      </c>
+      <c r="G107">
+        <v>100</v>
+      </c>
+      <c r="H107" cm="1">
+        <f t="array" ref="H107:H110">_xlfn.XLOOKUP(E107, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>440</v>
+      </c>
+      <c r="I107" cm="1">
+        <f t="array" ref="I107:I110">_xlfn.XLOOKUP(E107, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.3</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="K107">
+        <v>1.3</v>
+      </c>
+      <c r="L107">
+        <f>(J107*K107)+(1 - J107)</f>
+        <v>1.3</v>
+      </c>
+      <c r="M107">
+        <f>(1.185 + 0.00454 * H107 - 0.0000026 * H107^2 + 0.315 * I107)^2 * L107</f>
+        <v>10.001723663880002</v>
+      </c>
+      <c r="N107">
+        <f>(M107 * (1 -S$11) + (0.04 * M107)) * ( 1 - AD$11 )</f>
+        <v>4.1167094600530074</v>
+      </c>
+      <c r="O107">
+        <f t="shared" si="13"/>
+        <v>1.9367899463549227E-4</v>
+      </c>
+      <c r="P107">
+        <f>N107 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.3188416618002772E-3</v>
+      </c>
+      <c r="Q107">
+        <f t="shared" si="14"/>
+        <v>1.7673208260488671</v>
+      </c>
+      <c r="R107">
+        <f t="shared" si="15"/>
+        <v>21.159430163927528</v>
+      </c>
       <c r="AM107" t="s">
         <v>53</v>
       </c>
@@ -5368,7 +7770,53 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="108" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="108" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F108" t="s">
+        <v>55</v>
+      </c>
+      <c r="G108">
+        <v>110</v>
+      </c>
+      <c r="H108">
+        <v>470</v>
+      </c>
+      <c r="I108">
+        <v>0.3</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L108">
+        <f t="shared" ref="L108:L114" si="16">(J108*K108)+(1 - J108)</f>
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <f t="shared" ref="M108:M130" si="17">(1.185 + 0.00454 * H108 - 0.0000026 * H108^2 + 0.315 * I108)^2 * L108</f>
+        <v>8.0596938816000012</v>
+      </c>
+      <c r="N108">
+        <f>(M108 * (1 -T$11) + (0.04 * M108)) * ( 1 - AD$11 )</f>
+        <v>2.6403557156121602</v>
+      </c>
+      <c r="O108">
+        <f t="shared" si="13"/>
+        <v>1.2422092096663393E-4</v>
+      </c>
+      <c r="P108">
+        <f>N108 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4872477386964117E-3</v>
+      </c>
+      <c r="Q108">
+        <f t="shared" si="14"/>
+        <v>1.2468674942025881</v>
+      </c>
+      <c r="R108">
+        <f t="shared" si="15"/>
+        <v>14.928249177165233</v>
+      </c>
       <c r="AO108" t="s">
         <v>55</v>
       </c>
@@ -5403,7 +7851,53 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="109" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="109" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F109" t="s">
+        <v>56</v>
+      </c>
+      <c r="G109">
+        <v>120</v>
+      </c>
+      <c r="H109">
+        <v>490</v>
+      </c>
+      <c r="I109">
+        <v>0.2</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="L109">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="M109">
+        <f t="shared" si="17"/>
+        <v>8.1130407556000002</v>
+      </c>
+      <c r="N109">
+        <f>(M109 * (1 -U$11) + (0.04 * M109)) * ( 1 - AD$11 )</f>
+        <v>2.99857986326976</v>
+      </c>
+      <c r="O109">
+        <f t="shared" si="13"/>
+        <v>1.4107430677044692E-4</v>
+      </c>
+      <c r="P109">
+        <f>N109 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6890266317448027E-3</v>
+      </c>
+      <c r="Q109">
+        <f t="shared" si="14"/>
+        <v>1.5447636591363938</v>
+      </c>
+      <c r="R109">
+        <f t="shared" si="15"/>
+        <v>18.494841617605591</v>
+      </c>
       <c r="AO109" t="s">
         <v>56</v>
       </c>
@@ -5438,7 +7932,53 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="110" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="110" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F110" t="s">
+        <v>57</v>
+      </c>
+      <c r="G110">
+        <v>130</v>
+      </c>
+      <c r="H110">
+        <v>500</v>
+      </c>
+      <c r="I110">
+        <v>0.1</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <f t="shared" si="17"/>
+        <v>8.0457322500000004</v>
+      </c>
+      <c r="N110">
+        <f>(M110 * (1 -V$11) + (0.04 * M110)) * ( 1 - AD$11 )</f>
+        <v>3.6495441486</v>
+      </c>
+      <c r="O110">
+        <f t="shared" si="13"/>
+        <v>1.7170024954095013E-4</v>
+      </c>
+      <c r="P110">
+        <f>N110 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.0556988780656223E-3</v>
+      </c>
+      <c r="Q110">
+        <f t="shared" si="14"/>
+        <v>2.0367942101795209</v>
+      </c>
+      <c r="R110">
+        <f t="shared" si="15"/>
+        <v>24.385727941053442</v>
+      </c>
       <c r="AO110" t="s">
         <v>57</v>
       </c>
@@ -5473,7 +8013,55 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="111" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="111" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E111" t="s">
+        <v>47</v>
+      </c>
+      <c r="F111" t="s">
+        <v>54</v>
+      </c>
+      <c r="H111" cm="1">
+        <f t="array" ref="H111:H114">_xlfn.XLOOKUP(E111, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>440</v>
+      </c>
+      <c r="I111" cm="1">
+        <f t="array" ref="I111:I114">_xlfn.XLOOKUP(E111, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.3</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>1.3</v>
+      </c>
+      <c r="L111">
+        <f t="shared" si="16"/>
+        <v>1.3</v>
+      </c>
+      <c r="M111">
+        <f t="shared" si="17"/>
+        <v>10.001723663880002</v>
+      </c>
+      <c r="N111">
+        <f>(M111 * (1 -S$11) + (0.04 * M111)) * ( 1 - AD$11 )</f>
+        <v>4.1167094600530074</v>
+      </c>
+      <c r="O111">
+        <f t="shared" si="13"/>
+        <v>1.9367899463549227E-4</v>
+      </c>
+      <c r="P111">
+        <f>N111 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.3188416618002772E-3</v>
+      </c>
+      <c r="Q111">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R111">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AM111" t="s">
         <v>59</v>
       </c>
@@ -5511,7 +8099,50 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="112" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="112" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F112" t="s">
+        <v>55</v>
+      </c>
+      <c r="H112">
+        <v>470</v>
+      </c>
+      <c r="I112">
+        <v>0.3</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L112">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <f t="shared" si="17"/>
+        <v>8.0596938816000012</v>
+      </c>
+      <c r="N112">
+        <f>(M112 * (1 -T$11) + (0.04 * M112)) * ( 1 - AD$11 )</f>
+        <v>2.6403557156121602</v>
+      </c>
+      <c r="O112">
+        <f t="shared" si="13"/>
+        <v>1.2422092096663393E-4</v>
+      </c>
+      <c r="P112">
+        <f>N112 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4872477386964117E-3</v>
+      </c>
+      <c r="Q112">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R112">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO112" t="s">
         <v>55</v>
       </c>
@@ -5546,7 +8177,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="113" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F113" t="s">
+        <v>56</v>
+      </c>
+      <c r="H113">
+        <v>490</v>
+      </c>
+      <c r="I113">
+        <v>0.2</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <f t="shared" si="17"/>
+        <v>8.1130407556000002</v>
+      </c>
+      <c r="N113">
+        <f>(M113 * (1 -U$11) + (0.04 * M113)) * ( 1 - AD$11 )</f>
+        <v>2.99857986326976</v>
+      </c>
+      <c r="O113">
+        <f t="shared" si="13"/>
+        <v>1.4107430677044692E-4</v>
+      </c>
+      <c r="P113">
+        <f>N113 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6890266317448027E-3</v>
+      </c>
+      <c r="Q113">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R113">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO113" t="s">
         <v>56</v>
       </c>
@@ -5581,7 +8255,50 @@
         <v>-0.22</v>
       </c>
     </row>
-    <row r="114" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="114" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F114" t="s">
+        <v>57</v>
+      </c>
+      <c r="H114">
+        <v>500</v>
+      </c>
+      <c r="I114">
+        <v>0.1</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <f t="shared" si="17"/>
+        <v>8.0457322500000004</v>
+      </c>
+      <c r="N114">
+        <f>(M114 * (1 -V$11) + (0.04 * M114)) * ( 1 - AD$11 )</f>
+        <v>3.6495441486</v>
+      </c>
+      <c r="O114">
+        <f t="shared" si="13"/>
+        <v>1.7170024954095013E-4</v>
+      </c>
+      <c r="P114">
+        <f>N114 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>2.0556988780656223E-3</v>
+      </c>
+      <c r="Q114">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R114">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO114" t="s">
         <v>57</v>
       </c>
@@ -5616,7 +8333,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="115" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E115" t="s">
+        <v>48</v>
+      </c>
+      <c r="F115" t="s">
+        <v>54</v>
+      </c>
+      <c r="G115">
+        <v>200</v>
+      </c>
+      <c r="H115" cm="1">
+        <f t="array" ref="H115:H118">_xlfn.XLOOKUP(E115, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>75</v>
+      </c>
+      <c r="I115" cm="1">
+        <f t="array" ref="I115:I118">_xlfn.XLOOKUP(E115, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.5</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <f t="shared" si="17"/>
+        <v>2.7834751406249998</v>
+      </c>
+      <c r="N115">
+        <f>(M115 * (1 -S$11) + (0.04 * M115)) * ( 1 - AD$11 )</f>
+        <v>1.1456783678812499</v>
+      </c>
+      <c r="O115">
+        <f t="shared" si="13"/>
+        <v>5.390077600084388E-5</v>
+      </c>
+      <c r="P115">
+        <f>N115 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>6.4533257842106233E-4</v>
+      </c>
+      <c r="Q115">
+        <f t="shared" si="14"/>
+        <v>0.98368916201540069</v>
+      </c>
+      <c r="R115">
+        <f t="shared" si="15"/>
+        <v>11.777319556184386</v>
+      </c>
       <c r="AM115" t="s">
         <v>69</v>
       </c>
@@ -5654,7 +8415,46 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="116" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="116" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F116" t="s">
+        <v>55</v>
+      </c>
+      <c r="G116">
+        <v>130</v>
+      </c>
+      <c r="H116">
+        <v>160</v>
+      </c>
+      <c r="I116">
+        <v>0.9</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <f t="shared" si="17"/>
+        <v>4.5298311556000002</v>
+      </c>
+      <c r="N116">
+        <f>(M116 * (1 -T$11) + (0.04 * M116)) * ( 1 - AD$11 )</f>
+        <v>1.4839726865745599</v>
+      </c>
+      <c r="O116">
+        <f t="shared" si="13"/>
+        <v>6.9816522344180778E-5</v>
+      </c>
+      <c r="P116">
+        <f>N116 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>8.3588548669608228E-4</v>
+      </c>
+      <c r="Q116">
+        <f t="shared" si="14"/>
+        <v>0.82819849630784437</v>
+      </c>
+      <c r="R116">
+        <f t="shared" si="15"/>
+        <v>9.9156915859322758</v>
+      </c>
       <c r="AO116" t="s">
         <v>55</v>
       </c>
@@ -5689,7 +8489,46 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="117" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="117" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F117" t="s">
+        <v>56</v>
+      </c>
+      <c r="G117">
+        <v>250</v>
+      </c>
+      <c r="H117">
+        <v>220</v>
+      </c>
+      <c r="I117">
+        <v>0.7</v>
+      </c>
+      <c r="L117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <f t="shared" si="17"/>
+        <v>5.1913799715999973</v>
+      </c>
+      <c r="N117">
+        <f>(M117 * (1 -U$11) + (0.04 * M117)) * ( 1 - AD$11 )</f>
+        <v>1.918734037503359</v>
+      </c>
+      <c r="O117">
+        <f t="shared" si="13"/>
+        <v>9.0270757011782037E-5</v>
+      </c>
+      <c r="P117">
+        <f>N117 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.0807759127164039E-3</v>
+      </c>
+      <c r="Q117">
+        <f t="shared" si="14"/>
+        <v>2.0593016443312777</v>
+      </c>
+      <c r="R117">
+        <f t="shared" si="15"/>
+        <v>24.655200508842963</v>
+      </c>
       <c r="AO117" t="s">
         <v>56</v>
       </c>
@@ -5724,7 +8563,46 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="118" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="118" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F118" t="s">
+        <v>57</v>
+      </c>
+      <c r="G118">
+        <v>150</v>
+      </c>
+      <c r="H118">
+        <v>260</v>
+      </c>
+      <c r="I118">
+        <v>0.4</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <f t="shared" si="17"/>
+        <v>5.3621886096000004</v>
+      </c>
+      <c r="N118">
+        <f>(M118 * (1 -V$11) + (0.04 * M118)) * ( 1 - AD$11 )</f>
+        <v>2.4322887533145603</v>
+      </c>
+      <c r="O118">
+        <f t="shared" si="13"/>
+        <v>1.1443198626874025E-4</v>
+      </c>
+      <c r="P118">
+        <f>N118 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.3700487123134107E-3</v>
+      </c>
+      <c r="Q118">
+        <f t="shared" si="14"/>
+        <v>1.5662878120533821</v>
+      </c>
+      <c r="R118">
+        <f t="shared" si="15"/>
+        <v>18.75254174978981</v>
+      </c>
       <c r="AO118" t="s">
         <v>57</v>
       </c>
@@ -5759,7 +8637,48 @@
         <v>-0.22</v>
       </c>
     </row>
-    <row r="119" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="119" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E119" t="s">
+        <v>49</v>
+      </c>
+      <c r="F119" t="s">
+        <v>54</v>
+      </c>
+      <c r="H119" cm="1">
+        <f t="array" ref="H119:H122">_xlfn.XLOOKUP(E119, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>380</v>
+      </c>
+      <c r="I119" cm="1">
+        <f t="array" ref="I119:I122">_xlfn.XLOOKUP(E119, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <f t="shared" si="17"/>
+        <v>7.0796437775999967</v>
+      </c>
+      <c r="N119">
+        <f>(M119 * (1 -S$11) + (0.04 * M119)) * ( 1 - AD$11 )</f>
+        <v>2.9139813788601581</v>
+      </c>
+      <c r="O119">
+        <f t="shared" si="13"/>
+        <v>1.37094198490489E-4</v>
+      </c>
+      <c r="P119">
+        <f>N119 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6413743764477724E-3</v>
+      </c>
+      <c r="Q119">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R119">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AM119" t="s">
         <v>70</v>
       </c>
@@ -5797,7 +8716,43 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="120" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="120" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F120" t="s">
+        <v>55</v>
+      </c>
+      <c r="H120">
+        <v>420</v>
+      </c>
+      <c r="I120">
+        <v>0.4</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <f t="shared" si="17"/>
+        <v>7.6129639056</v>
+      </c>
+      <c r="N120">
+        <f>(M120 * (1 -T$11) + (0.04 * M120)) * ( 1 - AD$11 )</f>
+        <v>2.49400697547456</v>
+      </c>
+      <c r="O120">
+        <f t="shared" si="13"/>
+        <v>1.1733564593543065E-4</v>
+      </c>
+      <c r="P120">
+        <f>N120 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4048130759940598E-3</v>
+      </c>
+      <c r="Q120">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R120">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO120" t="s">
         <v>55</v>
       </c>
@@ -5832,7 +8787,43 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="121" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="121" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F121" t="s">
+        <v>56</v>
+      </c>
+      <c r="H121">
+        <v>450</v>
+      </c>
+      <c r="I121">
+        <v>0.3</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <f t="shared" si="17"/>
+        <v>7.8176159999999992</v>
+      </c>
+      <c r="N121">
+        <f>(M121 * (1 -U$11) + (0.04 * M121)) * ( 1 - AD$11 )</f>
+        <v>2.8893908736</v>
+      </c>
+      <c r="O121">
+        <f t="shared" si="13"/>
+        <v>1.3593728800589413E-4</v>
+      </c>
+      <c r="P121">
+        <f>N121 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.627523146810294E-3</v>
+      </c>
+      <c r="Q121">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R121">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO121" t="s">
         <v>56</v>
       </c>
@@ -5867,7 +8858,43 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="122" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="122" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F122" t="s">
+        <v>57</v>
+      </c>
+      <c r="H122">
+        <v>460</v>
+      </c>
+      <c r="I122">
+        <v>0.1</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <f t="shared" si="17"/>
+        <v>7.5885924675999998</v>
+      </c>
+      <c r="N122">
+        <f>(M122 * (1 -V$11) + (0.04 * M122)) * ( 1 - AD$11 )</f>
+        <v>3.4421855433033599</v>
+      </c>
+      <c r="O122">
+        <f t="shared" si="13"/>
+        <v>1.6194464094321492E-4</v>
+      </c>
+      <c r="P122">
+        <f>N122 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.9388988518406825E-3</v>
+      </c>
+      <c r="Q122">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R122">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO122" t="s">
         <v>57</v>
       </c>
@@ -5902,7 +8929,48 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="123" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="123" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E123" t="s">
+        <v>50</v>
+      </c>
+      <c r="F123" t="s">
+        <v>54</v>
+      </c>
+      <c r="H123" cm="1">
+        <f t="array" ref="H123:H126">_xlfn.XLOOKUP(E123, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>380</v>
+      </c>
+      <c r="I123" cm="1">
+        <f t="array" ref="I123:I126">_xlfn.XLOOKUP(E123, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <f t="shared" si="17"/>
+        <v>7.0796437775999967</v>
+      </c>
+      <c r="N123">
+        <f>(M123 * (1 -S$11) + (0.04 * M123)) * ( 1 - AD$11 )</f>
+        <v>2.9139813788601581</v>
+      </c>
+      <c r="O123">
+        <f t="shared" si="13"/>
+        <v>1.37094198490489E-4</v>
+      </c>
+      <c r="P123">
+        <f>N123 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6413743764477724E-3</v>
+      </c>
+      <c r="Q123">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R123">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AM123" t="s">
         <v>65</v>
       </c>
@@ -5943,7 +9011,43 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="124" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="124" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F124" t="s">
+        <v>55</v>
+      </c>
+      <c r="H124">
+        <v>420</v>
+      </c>
+      <c r="I124">
+        <v>0.4</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <f t="shared" si="17"/>
+        <v>7.6129639056</v>
+      </c>
+      <c r="N124">
+        <f>(M124 * (1 -T$11) + (0.04 * M124)) * ( 1 - AD$11 )</f>
+        <v>2.49400697547456</v>
+      </c>
+      <c r="O124">
+        <f t="shared" si="13"/>
+        <v>1.1733564593543065E-4</v>
+      </c>
+      <c r="P124">
+        <f>N124 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4048130759940598E-3</v>
+      </c>
+      <c r="Q124">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R124">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO124" t="s">
         <v>55</v>
       </c>
@@ -5978,7 +9082,43 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="125" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="125" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F125" t="s">
+        <v>56</v>
+      </c>
+      <c r="H125">
+        <v>450</v>
+      </c>
+      <c r="I125">
+        <v>0.3</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="M125">
+        <f t="shared" si="17"/>
+        <v>7.8176159999999992</v>
+      </c>
+      <c r="N125">
+        <f>(M125 * (1 -U$11) + (0.04 * M125)) * ( 1 - AD$11 )</f>
+        <v>2.8893908736</v>
+      </c>
+      <c r="O125">
+        <f t="shared" si="13"/>
+        <v>1.3593728800589413E-4</v>
+      </c>
+      <c r="P125">
+        <f>N125 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.627523146810294E-3</v>
+      </c>
+      <c r="Q125">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R125">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO125" t="s">
         <v>56</v>
       </c>
@@ -6013,7 +9153,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="126" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F126" t="s">
+        <v>57</v>
+      </c>
+      <c r="H126">
+        <v>460</v>
+      </c>
+      <c r="I126">
+        <v>0.1</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <f t="shared" si="17"/>
+        <v>7.5885924675999998</v>
+      </c>
+      <c r="N126">
+        <f>(M126 * (1 -V$11) + (0.04 * M126)) * ( 1 - AD$11 )</f>
+        <v>3.4421855433033599</v>
+      </c>
+      <c r="O126">
+        <f t="shared" si="13"/>
+        <v>1.6194464094321492E-4</v>
+      </c>
+      <c r="P126">
+        <f>N126 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.9388988518406825E-3</v>
+      </c>
+      <c r="Q126">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R126">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO126" t="s">
         <v>57</v>
       </c>
@@ -6048,7 +9224,48 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="127" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="127" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E127" t="s">
+        <v>51</v>
+      </c>
+      <c r="F127" t="s">
+        <v>54</v>
+      </c>
+      <c r="H127" cm="1">
+        <f t="array" ref="H127:H130">_xlfn.XLOOKUP(E127, $AP$46:$AY$46, $AP$47:$AY$50)</f>
+        <v>380</v>
+      </c>
+      <c r="I127" cm="1">
+        <f t="array" ref="I127:I130">_xlfn.XLOOKUP(E127, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.4</v>
+      </c>
+      <c r="L127">
+        <v>1</v>
+      </c>
+      <c r="M127">
+        <f t="shared" si="17"/>
+        <v>7.0796437775999967</v>
+      </c>
+      <c r="N127">
+        <f>(M127 * (1 -S$11) + (0.04 * M127)) * ( 1 - AD$11 )</f>
+        <v>2.9139813788601581</v>
+      </c>
+      <c r="O127">
+        <f t="shared" si="13"/>
+        <v>1.37094198490489E-4</v>
+      </c>
+      <c r="P127">
+        <f>N127 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.6413743764477724E-3</v>
+      </c>
+      <c r="Q127">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R127">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AM127" t="s">
         <v>65</v>
       </c>
@@ -6089,7 +9306,43 @@
         <v>-0.22</v>
       </c>
     </row>
-    <row r="128" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="128" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F128" t="s">
+        <v>55</v>
+      </c>
+      <c r="H128">
+        <v>420</v>
+      </c>
+      <c r="I128">
+        <v>0.4</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128">
+        <f t="shared" si="17"/>
+        <v>7.6129639056</v>
+      </c>
+      <c r="N128">
+        <f>(M128 * (1 -T$11) + (0.04 * M128)) * ( 1 - AD$11 )</f>
+        <v>2.49400697547456</v>
+      </c>
+      <c r="O128">
+        <f t="shared" si="13"/>
+        <v>1.1733564593543065E-4</v>
+      </c>
+      <c r="P128">
+        <f>N128 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.4048130759940598E-3</v>
+      </c>
+      <c r="Q128">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R128">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO128" t="s">
         <v>55</v>
       </c>
@@ -6124,7 +9377,43 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="129" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F129" t="s">
+        <v>56</v>
+      </c>
+      <c r="H129">
+        <v>450</v>
+      </c>
+      <c r="I129">
+        <v>0.3</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129">
+        <f t="shared" si="17"/>
+        <v>7.8176159999999992</v>
+      </c>
+      <c r="N129">
+        <f>(M129 * (1 -U$11) + (0.04 * M129)) * ( 1 - AD$11 )</f>
+        <v>2.8893908736</v>
+      </c>
+      <c r="O129">
+        <f t="shared" si="13"/>
+        <v>1.3593728800589413E-4</v>
+      </c>
+      <c r="P129">
+        <f>N129 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.627523146810294E-3</v>
+      </c>
+      <c r="Q129">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R129">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO129" t="s">
         <v>56</v>
       </c>
@@ -6159,7 +9448,43 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="130" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F130" t="s">
+        <v>57</v>
+      </c>
+      <c r="H130">
+        <v>460</v>
+      </c>
+      <c r="I130">
+        <v>0.1</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="M130">
+        <f t="shared" si="17"/>
+        <v>7.5885924675999998</v>
+      </c>
+      <c r="N130">
+        <f>(M130 * (1 -V$11) + (0.04 * M130)) * ( 1 - AD$11 )</f>
+        <v>3.4421855433033599</v>
+      </c>
+      <c r="O130">
+        <f t="shared" si="13"/>
+        <v>1.6194464094321492E-4</v>
+      </c>
+      <c r="P130">
+        <f>N130 * AB$11 * Y$11 * AA$11 * AC$11</f>
+        <v>1.9388988518406825E-3</v>
+      </c>
+      <c r="Q130">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AO130" t="s">
         <v>57</v>
       </c>
@@ -6194,7 +9519,7 @@
         <v>-0.33</v>
       </c>
     </row>
-    <row r="131" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AM131" t="s">
         <v>65</v>
       </c>
@@ -6235,7 +9560,7 @@
         <v>-0.55000000000000004</v>
       </c>
     </row>
-    <row r="132" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AO132" t="s">
         <v>55</v>
       </c>
@@ -6270,7 +9595,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="133" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AO133" t="s">
         <v>56</v>
       </c>
@@ -6305,7 +9630,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="134" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AO134" t="s">
         <v>57</v>
       </c>
@@ -6340,7 +9665,7 @@
         <v>-0.55000000000000004</v>
       </c>
     </row>
-    <row r="135" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AM135" t="s">
         <v>73</v>
       </c>
@@ -6381,7 +9706,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="136" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AO136" t="s">
         <v>55</v>
       </c>
@@ -6416,7 +9741,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="137" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AO137" t="s">
         <v>56</v>
       </c>
@@ -6451,7 +9776,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="138" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AO138" t="s">
         <v>57</v>
       </c>
@@ -6486,7 +9811,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="139" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AM139" t="s">
         <v>73</v>
       </c>
@@ -6527,7 +9852,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="140" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:51" x14ac:dyDescent="0.2">
       <c r="AO140" t="s">
         <v>55</v>
       </c>
@@ -6562,7 +9887,119 @@
         <v>72</v>
       </c>
     </row>
-    <row r="141" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>117</v>
+      </c>
+      <c r="B141" t="s">
+        <v>99</v>
+      </c>
+      <c r="C141" t="s">
+        <v>53</v>
+      </c>
+      <c r="D141" t="s">
+        <v>53</v>
+      </c>
+      <c r="E141" t="s">
+        <v>42</v>
+      </c>
+      <c r="F141" t="s">
+        <v>54</v>
+      </c>
+      <c r="G141">
+        <v>100</v>
+      </c>
+      <c r="H141" s="8">
+        <v>80</v>
+      </c>
+      <c r="I141" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="M141">
+        <f>(1.185 + 0.00454 * H141 - 0.0000026 * H141^2 + 0.315 * I141)^2 * L141</f>
+        <v>2.7475051536000006</v>
+      </c>
+      <c r="N141">
+        <f>(M141 * (1 -S$141) + (0.04 * M141)) * ( 1 - AD$141 )</f>
+        <v>1.0154779047705602</v>
+      </c>
+      <c r="O141">
+        <f>N141 * AB$141 * X$141 * Z$141 * AC$141</f>
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <f>N141 * AB$141 * Y$141 * AA$141 * AC$141</f>
+        <v>6.0209878406120823E-4</v>
+      </c>
+      <c r="Q141">
+        <f>G141*O141*91.25</f>
+        <v>0</v>
+      </c>
+      <c r="R141">
+        <f>G141*P141*91.25</f>
+        <v>5.4941514045585258</v>
+      </c>
+      <c r="S141" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="T141" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="U141" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V141" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="W141" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="X141">
+        <f>IF(W141="yes", $AN$6, $AO$6)</f>
+        <v>0</v>
+      </c>
+      <c r="Y141">
+        <f>IF(W141="yes", $AN$7, $AO$7)</f>
+        <v>1</v>
+      </c>
+      <c r="Z141">
+        <f>VLOOKUP(B141, $AZ$17:$BA$26, 2, FALSE)</f>
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="AA141">
+        <f>$BA$14</f>
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="AB141">
+        <f>$AS$5</f>
+        <v>0.19</v>
+      </c>
+      <c r="AC141">
+        <f>$AS$6</f>
+        <v>0.6784</v>
+      </c>
+      <c r="AD141">
+        <f>$AS$7</f>
+        <v>0.16</v>
+      </c>
+      <c r="AE141">
+        <f>SUM(Q141:R180)</f>
+        <v>487.70821373357535</v>
+      </c>
+      <c r="AF141">
+        <f>$AS$8</f>
+        <v>28</v>
+      </c>
+      <c r="AG141">
+        <f>AE141 * AF141 * 10^-3</f>
+        <v>13.655829984540109</v>
+      </c>
       <c r="AO141" t="s">
         <v>56</v>
       </c>
@@ -6597,7 +10034,46 @@
         <v>72</v>
       </c>
     </row>
-    <row r="142" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F142" t="s">
+        <v>55</v>
+      </c>
+      <c r="G142">
+        <v>110</v>
+      </c>
+      <c r="H142" s="8">
+        <v>90</v>
+      </c>
+      <c r="I142" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="L142">
+        <v>1</v>
+      </c>
+      <c r="M142">
+        <f t="shared" ref="M142:M156" si="18">(1.185 + 0.00454 * H142 - 0.0000026 * H142^2 + 0.315 * I142)^2 * L142</f>
+        <v>2.8850381316</v>
+      </c>
+      <c r="N142">
+        <f>(M142 * (1 -T$141) + (0.04 * M142)) * ( 1 - AD$141 )</f>
+        <v>0.82396689038496007</v>
+      </c>
+      <c r="O142">
+        <f t="shared" ref="O142:O180" si="19">N142 * AB$141 * X$141 * Z$141 * AC$141</f>
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <f t="shared" ref="P142:P180" si="20">N142 * AB$141 * Y$141 * AA$141 * AC$141</f>
+        <v>4.8854776699407511E-4</v>
+      </c>
+      <c r="Q142">
+        <f t="shared" ref="Q142:Q180" si="21">G142*O142*91.25</f>
+        <v>0</v>
+      </c>
+      <c r="R142">
+        <f t="shared" ref="R142:R180" si="22">G142*P142*91.25</f>
+        <v>4.9037982112030285</v>
+      </c>
       <c r="AO142" t="s">
         <v>57</v>
       </c>
@@ -6632,7 +10108,46 @@
         <v>72</v>
       </c>
     </row>
-    <row r="143" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F143" t="s">
+        <v>56</v>
+      </c>
+      <c r="G143">
+        <v>120</v>
+      </c>
+      <c r="H143" s="8">
+        <v>100</v>
+      </c>
+      <c r="I143" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="M143">
+        <f t="shared" si="18"/>
+        <v>3.1346702499999997</v>
+      </c>
+      <c r="N143">
+        <f>(M143 * (1 -U$141) + (0.04 * M143)) * ( 1 - AD$141 )</f>
+        <v>1.4218864253999999</v>
+      </c>
+      <c r="O143">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <f t="shared" si="20"/>
+        <v>8.4306717436644866E-4</v>
+      </c>
+      <c r="Q143">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R143">
+        <f t="shared" si="22"/>
+        <v>9.231585559312613</v>
+      </c>
       <c r="AM143" t="s">
         <v>73</v>
       </c>
@@ -6673,7 +10188,46 @@
         <v>72</v>
       </c>
     </row>
-    <row r="144" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="F144" t="s">
+        <v>57</v>
+      </c>
+      <c r="G144">
+        <v>130</v>
+      </c>
+      <c r="H144" s="8">
+        <v>110</v>
+      </c>
+      <c r="I144" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="L144">
+        <v>1</v>
+      </c>
+      <c r="M144">
+        <f t="shared" si="18"/>
+        <v>3.6287964036000004</v>
+      </c>
+      <c r="N144">
+        <f>(M144 * (1 -V$141) + (0.04 * M144)) * ( 1 - AD$141 )</f>
+        <v>1.95084094657536</v>
+      </c>
+      <c r="O144">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <f t="shared" si="20"/>
+        <v>1.156695735388977E-3</v>
+      </c>
+      <c r="Q144">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R144">
+        <f t="shared" si="22"/>
+        <v>13.72130316105174</v>
+      </c>
       <c r="AO144" t="s">
         <v>55</v>
       </c>
@@ -6708,7 +10262,49 @@
         <v>72</v>
       </c>
     </row>
-    <row r="145" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="145" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E145" t="s">
+        <v>43</v>
+      </c>
+      <c r="F145" t="s">
+        <v>54</v>
+      </c>
+      <c r="G145">
+        <v>50</v>
+      </c>
+      <c r="H145" s="8">
+        <v>470</v>
+      </c>
+      <c r="I145" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145">
+        <f t="shared" si="18"/>
+        <v>7.7059539215999999</v>
+      </c>
+      <c r="N145">
+        <f t="shared" ref="N145" si="23">(M145 * (1 -S$141) + (0.04 * M145)) * ( 1 - AD$141 )</f>
+        <v>2.8481205694233598</v>
+      </c>
+      <c r="O145">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <f t="shared" si="20"/>
+        <v>1.6887122050154094E-3</v>
+      </c>
+      <c r="Q145">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R145">
+        <f t="shared" si="22"/>
+        <v>7.704749435382805</v>
+      </c>
       <c r="AO145" t="s">
         <v>56</v>
       </c>
@@ -6743,7 +10339,46 @@
         <v>72</v>
       </c>
     </row>
-    <row r="146" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="146" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F146" t="s">
+        <v>55</v>
+      </c>
+      <c r="G146">
+        <v>55</v>
+      </c>
+      <c r="H146" s="8">
+        <v>480</v>
+      </c>
+      <c r="I146" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="L146">
+        <v>1</v>
+      </c>
+      <c r="M146">
+        <f t="shared" si="18"/>
+        <v>7.9984889855999999</v>
+      </c>
+      <c r="N146">
+        <f t="shared" ref="N146" si="24">(M146 * (1 -T$141) + (0.04 * M146)) * ( 1 - AD$141 )</f>
+        <v>2.2843684542873599</v>
+      </c>
+      <c r="O146">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <f t="shared" si="20"/>
+        <v>1.3544513989055885E-3</v>
+      </c>
+      <c r="Q146">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R146">
+        <f t="shared" si="22"/>
+        <v>6.797652958257423</v>
+      </c>
       <c r="AO146" t="s">
         <v>57</v>
       </c>
@@ -6778,7 +10413,46 @@
         <v>72</v>
       </c>
     </row>
-    <row r="147" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="147" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F147" t="s">
+        <v>56</v>
+      </c>
+      <c r="G147">
+        <v>60</v>
+      </c>
+      <c r="H147" s="8">
+        <v>490</v>
+      </c>
+      <c r="I147" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <f t="shared" si="18"/>
+        <v>10.6135214656</v>
+      </c>
+      <c r="N147">
+        <f t="shared" ref="N147" si="25">(M147 * (1 -U$141) + (0.04 * M147)) * ( 1 - AD$141 )</f>
+        <v>4.81429333679616</v>
+      </c>
+      <c r="O147">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <f t="shared" si="20"/>
+        <v>2.8544985081225176E-3</v>
+      </c>
+      <c r="Q147">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R147">
+        <f t="shared" si="22"/>
+        <v>15.628379331970782</v>
+      </c>
       <c r="AM147" t="s">
         <v>81</v>
       </c>
@@ -6819,7 +10493,46 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="148" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="148" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F148" t="s">
+        <v>57</v>
+      </c>
+      <c r="G148">
+        <v>65</v>
+      </c>
+      <c r="H148" s="8">
+        <v>500</v>
+      </c>
+      <c r="I148" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="L148">
+        <v>1</v>
+      </c>
+      <c r="M148">
+        <f t="shared" si="18"/>
+        <v>10.333010250000001</v>
+      </c>
+      <c r="N148">
+        <f t="shared" ref="N148" si="26">(M148 * (1 -V$141) + (0.04 * M148)) * ( 1 - AD$141 )</f>
+        <v>5.5550263103999997</v>
+      </c>
+      <c r="O148">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <f t="shared" si="20"/>
+        <v>3.2936950880044645E-3</v>
+      </c>
+      <c r="Q148">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R148">
+        <f t="shared" si="22"/>
+        <v>19.535728990726483</v>
+      </c>
       <c r="AO148" t="s">
         <v>55</v>
       </c>
@@ -6854,7 +10567,49 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="149" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="149" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E149" t="s">
+        <v>44</v>
+      </c>
+      <c r="F149" t="s">
+        <v>54</v>
+      </c>
+      <c r="G149">
+        <v>200</v>
+      </c>
+      <c r="H149" s="8">
+        <v>70</v>
+      </c>
+      <c r="I149" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="L149">
+        <v>1</v>
+      </c>
+      <c r="M149">
+        <f t="shared" si="18"/>
+        <v>2.6116499236000004</v>
+      </c>
+      <c r="N149">
+        <f t="shared" ref="N149" si="27">(M149 * (1 -S$141) + (0.04 * M149)) * ( 1 - AD$141 )</f>
+        <v>0.96526581176256021</v>
+      </c>
+      <c r="O149">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <f t="shared" si="20"/>
+        <v>5.7232694953555604E-4</v>
+      </c>
+      <c r="Q149">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R149">
+        <f t="shared" si="22"/>
+        <v>10.444966829023898</v>
+      </c>
       <c r="AO149" t="s">
         <v>56</v>
       </c>
@@ -6889,7 +10644,46 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="150" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="150" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F150" t="s">
+        <v>55</v>
+      </c>
+      <c r="G150">
+        <v>130</v>
+      </c>
+      <c r="H150" s="8">
+        <v>75</v>
+      </c>
+      <c r="I150" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <f t="shared" si="18"/>
+        <v>2.7834751406249998</v>
+      </c>
+      <c r="N150">
+        <f t="shared" ref="N150" si="28">(M150 * (1 -T$141) + (0.04 * M150)) * ( 1 - AD$141 )</f>
+        <v>0.79496050016249997</v>
+      </c>
+      <c r="O150">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <f t="shared" si="20"/>
+        <v>4.7134925169314975E-4</v>
+      </c>
+      <c r="Q150">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R150">
+        <f t="shared" si="22"/>
+        <v>5.5913804982099888</v>
+      </c>
       <c r="AO150" t="s">
         <v>57</v>
       </c>
@@ -6924,7 +10718,46 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="151" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="151" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F151" t="s">
+        <v>56</v>
+      </c>
+      <c r="G151">
+        <v>250</v>
+      </c>
+      <c r="H151" s="8">
+        <v>80</v>
+      </c>
+      <c r="I151" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="L151">
+        <v>1</v>
+      </c>
+      <c r="M151">
+        <f t="shared" si="18"/>
+        <v>2.9603267136000002</v>
+      </c>
+      <c r="N151">
+        <f t="shared" ref="N151" si="29">(M151 * (1 -U$141) + (0.04 * M151)) * ( 1 - AD$141 )</f>
+        <v>1.3428041972889599</v>
+      </c>
+      <c r="O151">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <f t="shared" si="20"/>
+        <v>7.9617761314328584E-4</v>
+      </c>
+      <c r="Q151">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R151">
+        <f t="shared" si="22"/>
+        <v>18.162801799831207</v>
+      </c>
       <c r="AM151" t="s">
         <v>81</v>
       </c>
@@ -6965,7 +10798,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="152" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F152" t="s">
+        <v>57</v>
+      </c>
+      <c r="G152">
+        <v>150</v>
+      </c>
+      <c r="H152" s="8">
+        <v>85</v>
+      </c>
+      <c r="I152" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="L152">
+        <v>1</v>
+      </c>
+      <c r="M152">
+        <f t="shared" si="18"/>
+        <v>3.1421639382249995</v>
+      </c>
+      <c r="N152">
+        <f t="shared" ref="N152" si="30">(M152 * (1 -V$141) + (0.04 * M152)) * ( 1 - AD$141 )</f>
+        <v>1.6892273331897594</v>
+      </c>
+      <c r="O152">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <f t="shared" si="20"/>
+        <v>1.0015793731586052E-3</v>
+      </c>
+      <c r="Q152">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R152">
+        <f t="shared" si="22"/>
+        <v>13.709117670108409</v>
+      </c>
       <c r="AO152" t="s">
         <v>55</v>
       </c>
@@ -7000,7 +10872,49 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="153" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="153" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E153" t="s">
+        <v>45</v>
+      </c>
+      <c r="F153" t="s">
+        <v>54</v>
+      </c>
+      <c r="G153">
+        <v>20</v>
+      </c>
+      <c r="H153" s="8">
+        <v>310</v>
+      </c>
+      <c r="I153" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
+      <c r="M153">
+        <f t="shared" si="18"/>
+        <v>6.2502000016000014</v>
+      </c>
+      <c r="N153">
+        <f t="shared" ref="N153" si="31">(M153 * (1 -S$141) + (0.04 * M153)) * ( 1 - AD$141 )</f>
+        <v>2.3100739205913605</v>
+      </c>
+      <c r="O153">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <f t="shared" si="20"/>
+        <v>1.3696927251153025E-3</v>
+      </c>
+      <c r="Q153">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R153">
+        <f t="shared" si="22"/>
+        <v>2.4996892233354271</v>
+      </c>
       <c r="AO153" t="s">
         <v>56</v>
       </c>
@@ -7035,7 +10949,46 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="154" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="154" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F154" t="s">
+        <v>55</v>
+      </c>
+      <c r="G154">
+        <v>30</v>
+      </c>
+      <c r="H154" s="8">
+        <v>320</v>
+      </c>
+      <c r="I154" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="M154">
+        <f t="shared" si="18"/>
+        <v>6.2378059535999979</v>
+      </c>
+      <c r="N154">
+        <f t="shared" ref="N154" si="32">(M154 * (1 -T$141) + (0.04 * M154)) * ( 1 - AD$141 )</f>
+        <v>1.7815173803481597</v>
+      </c>
+      <c r="O154">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <f t="shared" si="20"/>
+        <v>1.0563001355838395E-3</v>
+      </c>
+      <c r="Q154">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R154">
+        <f t="shared" si="22"/>
+        <v>2.8916216211607608</v>
+      </c>
       <c r="AO154" t="s">
         <v>57</v>
       </c>
@@ -7070,7 +11023,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="155" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F155" t="s">
+        <v>56</v>
+      </c>
+      <c r="G155">
+        <v>60</v>
+      </c>
+      <c r="H155" s="8">
+        <v>330</v>
+      </c>
+      <c r="I155" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="L155">
+        <v>1</v>
+      </c>
+      <c r="M155">
+        <f t="shared" si="18"/>
+        <v>6.222829593600002</v>
+      </c>
+      <c r="N155">
+        <f t="shared" ref="N155" si="33">(M155 * (1 -U$141) + (0.04 * M155)) * ( 1 - AD$141 )</f>
+        <v>2.8226755036569608</v>
+      </c>
+      <c r="O155">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <f t="shared" si="20"/>
+        <v>1.6736252759090909E-3</v>
+      </c>
+      <c r="Q155">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R155">
+        <f t="shared" si="22"/>
+        <v>9.1630983856022716</v>
+      </c>
       <c r="AM155" t="s">
         <v>81</v>
       </c>
@@ -7111,7 +11103,46 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="156" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="156" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F156" t="s">
+        <v>57</v>
+      </c>
+      <c r="G156">
+        <v>30</v>
+      </c>
+      <c r="H156" s="8">
+        <v>340</v>
+      </c>
+      <c r="I156" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
+      </c>
+      <c r="M156">
+        <f t="shared" si="18"/>
+        <v>6.2052802816000021</v>
+      </c>
+      <c r="N156">
+        <f t="shared" ref="N156" si="34">(M156 * (1 -V$141) + (0.04 * M156)) * ( 1 - AD$141 )</f>
+        <v>3.3359586793881606</v>
+      </c>
+      <c r="O156">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <f t="shared" si="20"/>
+        <v>1.9779619577167153E-3</v>
+      </c>
+      <c r="Q156">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R156">
+        <f t="shared" si="22"/>
+        <v>5.4146708592495081</v>
+      </c>
       <c r="AO156" t="s">
         <v>55</v>
       </c>
@@ -7146,7 +11177,57 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="157" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="157" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E157" t="s">
+        <v>46</v>
+      </c>
+      <c r="F157" t="s">
+        <v>54</v>
+      </c>
+      <c r="G157">
+        <v>100</v>
+      </c>
+      <c r="H157" s="8">
+        <v>450</v>
+      </c>
+      <c r="I157" s="8" cm="1">
+        <f t="array" ref="I157:I160">_xlfn.XLOOKUP(E157, $AP$106:$AY$106, $AP$107:$AY$110)</f>
+        <v>0.3</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>1.3</v>
+      </c>
+      <c r="L157">
+        <f>(J157*K157)+(1 - J157)</f>
+        <v>1.3</v>
+      </c>
+      <c r="M157">
+        <f>(1.185 + 0.00454 * H157 - 0.0000026 * H157^2 + 0.315 * I157)^2 * L157</f>
+        <v>10.162900799999999</v>
+      </c>
+      <c r="N157">
+        <f t="shared" ref="N157" si="35">(M157 * (1 -S$141) + (0.04 * M157)) * ( 1 - AD$141 )</f>
+        <v>3.7562081356799992</v>
+      </c>
+      <c r="O157">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <f t="shared" si="20"/>
+        <v>2.2271369377404025E-3</v>
+      </c>
+      <c r="Q157">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R157">
+        <f t="shared" si="22"/>
+        <v>20.322624556881173</v>
+      </c>
       <c r="AO157" t="s">
         <v>56</v>
       </c>
@@ -7181,7 +11262,53 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="158" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="158" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F158" t="s">
+        <v>55</v>
+      </c>
+      <c r="G158">
+        <v>110</v>
+      </c>
+      <c r="H158" s="8">
+        <v>460</v>
+      </c>
+      <c r="I158" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L158">
+        <f t="shared" ref="L158:L164" si="36">(J158*K158)+(1 - J158)</f>
+        <v>1</v>
+      </c>
+      <c r="M158">
+        <f t="shared" ref="M158:M180" si="37">(1.185 + 0.00454 * H158 - 0.0000026 * H158^2 + 0.315 * I158)^2 * L158</f>
+        <v>7.9396587076000005</v>
+      </c>
+      <c r="N158">
+        <f t="shared" ref="N158" si="38">(M158 * (1 -T$141) + (0.04 * M158)) * ( 1 - AD$141 )</f>
+        <v>2.2675665268905605</v>
+      </c>
+      <c r="O158">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <f t="shared" si="20"/>
+        <v>1.3444891732303941E-3</v>
+      </c>
+      <c r="Q158">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R158">
+        <f t="shared" si="22"/>
+        <v>13.495310076300081</v>
+      </c>
       <c r="AO158" t="s">
         <v>57</v>
       </c>
@@ -7216,7 +11343,53 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="159" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="159" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F159" t="s">
+        <v>56</v>
+      </c>
+      <c r="G159">
+        <v>120</v>
+      </c>
+      <c r="H159" s="8">
+        <v>470</v>
+      </c>
+      <c r="I159" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="L159">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+      <c r="M159">
+        <f t="shared" si="37"/>
+        <v>7.8818316516000015</v>
+      </c>
+      <c r="N159">
+        <f t="shared" ref="N159" si="39">(M159 * (1 -U$141) + (0.04 * M159)) * ( 1 - AD$141 )</f>
+        <v>3.5751988371657606</v>
+      </c>
+      <c r="O159">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P159">
+        <f t="shared" si="20"/>
+        <v>2.1198126148504622E-3</v>
+      </c>
+      <c r="Q159">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R159">
+        <f t="shared" si="22"/>
+        <v>23.211948132612562</v>
+      </c>
       <c r="AM159" t="s">
         <v>81</v>
       </c>
@@ -7257,7 +11430,53 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="160" spans="39:51" x14ac:dyDescent="0.2">
+    <row r="160" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F160" t="s">
+        <v>57</v>
+      </c>
+      <c r="G160">
+        <v>130</v>
+      </c>
+      <c r="H160" s="8">
+        <v>480</v>
+      </c>
+      <c r="I160" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+      <c r="M160">
+        <f t="shared" si="37"/>
+        <v>7.8213071555999987</v>
+      </c>
+      <c r="N160">
+        <f t="shared" ref="N160" si="40">(M160 * (1 -V$141) + (0.04 * M160)) * ( 1 - AD$141 )</f>
+        <v>4.2047347268505595</v>
+      </c>
+      <c r="O160">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P160">
+        <f t="shared" si="20"/>
+        <v>2.4930780418197965E-3</v>
+      </c>
+      <c r="Q160">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R160">
+        <f t="shared" si="22"/>
+        <v>29.574138271087339</v>
+      </c>
       <c r="AO160" t="s">
         <v>55</v>
       </c>
@@ -7292,7 +11511,56 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="161" spans="41:51" x14ac:dyDescent="0.2">
+    <row r="161" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E161" t="s">
+        <v>47</v>
+      </c>
+      <c r="F161" t="s">
+        <v>54</v>
+      </c>
+      <c r="G161">
+        <v>50</v>
+      </c>
+      <c r="H161" s="8">
+        <v>470</v>
+      </c>
+      <c r="I161" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161">
+        <v>1.3</v>
+      </c>
+      <c r="L161">
+        <f t="shared" si="36"/>
+        <v>1.3</v>
+      </c>
+      <c r="M161">
+        <f t="shared" si="37"/>
+        <v>10.477602046080001</v>
+      </c>
+      <c r="N161">
+        <f t="shared" ref="N161" si="41">(M161 * (1 -S$141) + (0.04 * M161)) * ( 1 - AD$141 )</f>
+        <v>3.872521716231168</v>
+      </c>
+      <c r="O161">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P161">
+        <f t="shared" si="20"/>
+        <v>2.2961017720225302E-3</v>
+      </c>
+      <c r="Q161">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R161">
+        <f t="shared" si="22"/>
+        <v>10.475964334852794</v>
+      </c>
       <c r="AO161" t="s">
         <v>56</v>
       </c>
@@ -7327,7 +11595,53 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="162" spans="41:51" x14ac:dyDescent="0.2">
+    <row r="162" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F162" t="s">
+        <v>55</v>
+      </c>
+      <c r="G162">
+        <v>55</v>
+      </c>
+      <c r="H162" s="8">
+        <v>480</v>
+      </c>
+      <c r="I162" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L162">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+      <c r="M162">
+        <f t="shared" si="37"/>
+        <v>8.3588061455999991</v>
+      </c>
+      <c r="N162">
+        <f t="shared" ref="N162" si="42">(M162 * (1 -T$141) + (0.04 * M162)) * ( 1 - AD$141 )</f>
+        <v>2.38727503518336</v>
+      </c>
+      <c r="O162">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <f t="shared" si="20"/>
+        <v>1.415466933500974E-3</v>
+      </c>
+      <c r="Q162">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R162">
+        <f t="shared" si="22"/>
+        <v>7.103874672508014</v>
+      </c>
       <c r="AO162" t="s">
         <v>57</v>
       </c>
@@ -7360,6 +11674,770 @@
       </c>
       <c r="AY162">
         <v>0.33</v>
+      </c>
+    </row>
+    <row r="163" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F163" t="s">
+        <v>56</v>
+      </c>
+      <c r="G163">
+        <v>60</v>
+      </c>
+      <c r="H163" s="8">
+        <v>490</v>
+      </c>
+      <c r="I163" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <f t="shared" si="37"/>
+        <v>8.6603072656000002</v>
+      </c>
+      <c r="N163">
+        <f t="shared" ref="N163" si="43">(M163 * (1 -U$141) + (0.04 * M163)) * ( 1 - AD$141 )</f>
+        <v>3.9283153756761604</v>
+      </c>
+      <c r="O163">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <f t="shared" si="20"/>
+        <v>2.3291830378505103E-3</v>
+      </c>
+      <c r="Q163">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R163">
+        <f t="shared" si="22"/>
+        <v>12.752277132231542</v>
+      </c>
+    </row>
+    <row r="164" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F164" t="s">
+        <v>57</v>
+      </c>
+      <c r="G164">
+        <v>65</v>
+      </c>
+      <c r="H164" s="8">
+        <v>500</v>
+      </c>
+      <c r="I164" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <f t="shared" si="36"/>
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <f t="shared" si="37"/>
+        <v>8.9640360000000019</v>
+      </c>
+      <c r="N164">
+        <f t="shared" ref="N164" si="44">(M164 * (1 -V$141) + (0.04 * M164)) * ( 1 - AD$141 )</f>
+        <v>4.8190657536000003</v>
+      </c>
+      <c r="O164">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <f t="shared" si="20"/>
+        <v>2.8573281771297177E-3</v>
+      </c>
+      <c r="Q164">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R164">
+        <f t="shared" si="22"/>
+        <v>16.947527750600639</v>
+      </c>
+    </row>
+    <row r="165" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E165" t="s">
+        <v>48</v>
+      </c>
+      <c r="F165" t="s">
+        <v>54</v>
+      </c>
+      <c r="G165">
+        <v>200</v>
+      </c>
+      <c r="H165" s="8">
+        <v>70</v>
+      </c>
+      <c r="I165" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <f t="shared" si="37"/>
+        <v>2.9260155136000003</v>
+      </c>
+      <c r="N165">
+        <f t="shared" ref="N165" si="45">(M165 * (1 -S$141) + (0.04 * M165)) * ( 1 - AD$141 )</f>
+        <v>1.08145533382656</v>
+      </c>
+      <c r="O165">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <f t="shared" si="20"/>
+        <v>6.4121822686097807E-4</v>
+      </c>
+      <c r="Q165">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R165">
+        <f t="shared" si="22"/>
+        <v>11.70223264021285</v>
+      </c>
+    </row>
+    <row r="166" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F166" t="s">
+        <v>55</v>
+      </c>
+      <c r="G166">
+        <v>130</v>
+      </c>
+      <c r="H166" s="8">
+        <v>75</v>
+      </c>
+      <c r="I166" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="L166">
+        <v>1</v>
+      </c>
+      <c r="M166">
+        <f t="shared" si="37"/>
+        <v>3.107728265625</v>
+      </c>
+      <c r="N166">
+        <f t="shared" ref="N166" si="46">(M166 * (1 -T$141) + (0.04 * M166)) * ( 1 - AD$141 )</f>
+        <v>0.88756719266250006</v>
+      </c>
+      <c r="O166">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <f t="shared" si="20"/>
+        <v>5.2625775998095775E-4</v>
+      </c>
+      <c r="Q166">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R166">
+        <f t="shared" si="22"/>
+        <v>6.2427326777741108</v>
+      </c>
+    </row>
+    <row r="167" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F167" t="s">
+        <v>56</v>
+      </c>
+      <c r="G167">
+        <v>250</v>
+      </c>
+      <c r="H167" s="8">
+        <v>100</v>
+      </c>
+      <c r="I167" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="L167">
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <f t="shared" si="37"/>
+        <v>3.5967122500000004</v>
+      </c>
+      <c r="N167">
+        <f t="shared" ref="N167" si="47">(M167 * (1 -U$141) + (0.04 * M167)) * ( 1 - AD$141 )</f>
+        <v>1.6314686766000002</v>
+      </c>
+      <c r="O167">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <f t="shared" si="20"/>
+        <v>9.6733301807955458E-4</v>
+      </c>
+      <c r="Q167">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R167">
+        <f t="shared" si="22"/>
+        <v>22.067284474939839</v>
+      </c>
+    </row>
+    <row r="168" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F168" t="s">
+        <v>57</v>
+      </c>
+      <c r="G168">
+        <v>150</v>
+      </c>
+      <c r="H168" s="8">
+        <v>105</v>
+      </c>
+      <c r="I168" s="8">
+        <v>1</v>
+      </c>
+      <c r="L168">
+        <v>1</v>
+      </c>
+      <c r="M168">
+        <f t="shared" si="37"/>
+        <v>3.7948403612249999</v>
+      </c>
+      <c r="N168">
+        <f t="shared" ref="N168" si="48">(M168 * (1 -V$141) + (0.04 * M168)) * ( 1 - AD$141 )</f>
+        <v>2.0401061781945597</v>
+      </c>
+      <c r="O168">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P168">
+        <f t="shared" si="20"/>
+        <v>1.2096230193450034E-3</v>
+      </c>
+      <c r="Q168">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R168">
+        <f t="shared" si="22"/>
+        <v>16.556715077284736</v>
+      </c>
+    </row>
+    <row r="169" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E169" t="s">
+        <v>49</v>
+      </c>
+      <c r="F169" t="s">
+        <v>54</v>
+      </c>
+      <c r="G169">
+        <v>20</v>
+      </c>
+      <c r="H169" s="8">
+        <v>350</v>
+      </c>
+      <c r="I169" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
+      </c>
+      <c r="M169">
+        <f t="shared" si="37"/>
+        <v>7.8512039999999974</v>
+      </c>
+      <c r="N169">
+        <f t="shared" ref="N169" si="49">(M169 * (1 -S$141) + (0.04 * M169)) * ( 1 - AD$141 )</f>
+        <v>2.9018049983999994</v>
+      </c>
+      <c r="O169">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <f t="shared" si="20"/>
+        <v>1.7205428625393249E-3</v>
+      </c>
+      <c r="Q169">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R169">
+        <f t="shared" si="22"/>
+        <v>3.1399907241342682</v>
+      </c>
+    </row>
+    <row r="170" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F170" t="s">
+        <v>55</v>
+      </c>
+      <c r="G170">
+        <v>30</v>
+      </c>
+      <c r="H170" s="8">
+        <v>360</v>
+      </c>
+      <c r="I170" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="M170">
+        <f t="shared" si="37"/>
+        <v>8.1821169936000011</v>
+      </c>
+      <c r="N170">
+        <f t="shared" ref="N170" si="50">(M170 * (1 -T$141) + (0.04 * M170)) * ( 1 - AD$141 )</f>
+        <v>2.3368126133721603</v>
+      </c>
+      <c r="O170">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <f t="shared" si="20"/>
+        <v>1.3855466736208025E-3</v>
+      </c>
+      <c r="Q170">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R170">
+        <f t="shared" si="22"/>
+        <v>3.7929340190369465</v>
+      </c>
+    </row>
+    <row r="171" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F171" t="s">
+        <v>56</v>
+      </c>
+      <c r="G171">
+        <v>60</v>
+      </c>
+      <c r="H171" s="8">
+        <v>350</v>
+      </c>
+      <c r="I171" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <f t="shared" si="37"/>
+        <v>8.2082249999999988</v>
+      </c>
+      <c r="N171">
+        <f t="shared" ref="N171" si="51">(M171 * (1 -U$141) + (0.04 * M171)) * ( 1 - AD$141 )</f>
+        <v>3.7232508599999994</v>
+      </c>
+      <c r="O171">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <f t="shared" si="20"/>
+        <v>2.2075958571125759E-3</v>
+      </c>
+      <c r="Q171">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R171">
+        <f t="shared" si="22"/>
+        <v>12.086587317691354</v>
+      </c>
+    </row>
+    <row r="172" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F172" t="s">
+        <v>57</v>
+      </c>
+      <c r="G172">
+        <v>30</v>
+      </c>
+      <c r="H172" s="8">
+        <v>340</v>
+      </c>
+      <c r="I172" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="L172">
+        <v>1</v>
+      </c>
+      <c r="M172">
+        <f t="shared" si="37"/>
+        <v>8.2313905215999998</v>
+      </c>
+      <c r="N172">
+        <f t="shared" ref="N172" si="52">(M172 * (1 -V$141) + (0.04 * M172)) * ( 1 - AD$141 )</f>
+        <v>4.4251955444121602</v>
+      </c>
+      <c r="O172">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <f t="shared" si="20"/>
+        <v>2.6237940225057291E-3</v>
+      </c>
+      <c r="Q172">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R172">
+        <f t="shared" si="22"/>
+        <v>7.1826361366094327</v>
+      </c>
+    </row>
+    <row r="173" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="E173" t="s">
+        <v>50</v>
+      </c>
+      <c r="F173" t="s">
+        <v>54</v>
+      </c>
+      <c r="G173">
+        <v>100</v>
+      </c>
+      <c r="H173" s="8">
+        <v>400</v>
+      </c>
+      <c r="I173" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <f t="shared" si="37"/>
+        <v>7.3495209999999993</v>
+      </c>
+      <c r="N173">
+        <f t="shared" ref="N173" si="53">(M173 * (1 -S$141) + (0.04 * M173)) * ( 1 - AD$141 )</f>
+        <v>2.7163829615999999</v>
+      </c>
+      <c r="O173">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <f t="shared" si="20"/>
+        <v>1.6106021318046105E-3</v>
+      </c>
+      <c r="Q173">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R173">
+        <f t="shared" si="22"/>
+        <v>14.69674445271707</v>
+      </c>
+    </row>
+    <row r="174" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F174" t="s">
+        <v>55</v>
+      </c>
+      <c r="G174">
+        <v>110</v>
+      </c>
+      <c r="H174" s="8">
+        <v>410</v>
+      </c>
+      <c r="I174" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="L174">
+        <v>1</v>
+      </c>
+      <c r="M174">
+        <f t="shared" si="37"/>
+        <v>7.3107507456000027</v>
+      </c>
+      <c r="N174">
+        <f t="shared" ref="N174" si="54">(M174 * (1 -T$141) + (0.04 * M174)) * ( 1 - AD$141 )</f>
+        <v>2.087950412943361</v>
+      </c>
+      <c r="O174">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P174">
+        <f t="shared" si="20"/>
+        <v>1.2379908995630384E-3</v>
+      </c>
+      <c r="Q174">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R174">
+        <f t="shared" si="22"/>
+        <v>12.426333654363997</v>
+      </c>
+    </row>
+    <row r="175" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F175" t="s">
+        <v>56</v>
+      </c>
+      <c r="G175">
+        <v>120</v>
+      </c>
+      <c r="H175" s="8">
+        <v>420</v>
+      </c>
+      <c r="I175" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <f t="shared" si="37"/>
+        <v>7.2692787456000021</v>
+      </c>
+      <c r="N175">
+        <f t="shared" ref="N175" si="55">(M175 * (1 -U$141) + (0.04 * M175)) * ( 1 - AD$141 )</f>
+        <v>3.2973448390041611</v>
+      </c>
+      <c r="O175">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P175">
+        <f t="shared" si="20"/>
+        <v>1.9550669776940898E-3</v>
+      </c>
+      <c r="Q175">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R175">
+        <f t="shared" si="22"/>
+        <v>21.407983405750283</v>
+      </c>
+    </row>
+    <row r="176" spans="5:51" x14ac:dyDescent="0.2">
+      <c r="F176" t="s">
+        <v>57</v>
+      </c>
+      <c r="G176">
+        <v>130</v>
+      </c>
+      <c r="H176" s="8">
+        <v>430</v>
+      </c>
+      <c r="I176" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <f t="shared" si="37"/>
+        <v>8.0966426116000001</v>
+      </c>
+      <c r="N176">
+        <f t="shared" ref="N176" si="56">(M176 * (1 -V$141) + (0.04 * M176)) * ( 1 - AD$141 )</f>
+        <v>4.35275506799616</v>
+      </c>
+      <c r="O176">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P176">
+        <f t="shared" si="20"/>
+        <v>2.580842499324392E-3</v>
+      </c>
+      <c r="Q176">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R176">
+        <f t="shared" si="22"/>
+        <v>30.6152441482356</v>
+      </c>
+    </row>
+    <row r="177" spans="5:18" x14ac:dyDescent="0.2">
+      <c r="E177" t="s">
+        <v>51</v>
+      </c>
+      <c r="F177" t="s">
+        <v>54</v>
+      </c>
+      <c r="G177">
+        <v>50</v>
+      </c>
+      <c r="H177" s="8">
+        <v>400</v>
+      </c>
+      <c r="I177" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <f t="shared" si="37"/>
+        <v>7.5213062500000012</v>
+      </c>
+      <c r="N177">
+        <f t="shared" ref="N177" si="57">(M177 * (1 -S$141) + (0.04 * M177)) * ( 1 - AD$141 )</f>
+        <v>2.7798747900000005</v>
+      </c>
+      <c r="O177">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P177">
+        <f t="shared" si="20"/>
+        <v>1.6482478082864641E-3</v>
+      </c>
+      <c r="Q177">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R177">
+        <f t="shared" si="22"/>
+        <v>7.5201306253069919</v>
+      </c>
+    </row>
+    <row r="178" spans="5:18" x14ac:dyDescent="0.2">
+      <c r="F178" t="s">
+        <v>55</v>
+      </c>
+      <c r="G178">
+        <v>55</v>
+      </c>
+      <c r="H178" s="8">
+        <v>420</v>
+      </c>
+      <c r="I178" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <f t="shared" si="37"/>
+        <v>7.7877832356000019</v>
+      </c>
+      <c r="N178">
+        <f t="shared" ref="N178" si="58">(M178 * (1 -T$141) + (0.04 * M178)) * ( 1 - AD$141 )</f>
+        <v>2.2241908920873605</v>
+      </c>
+      <c r="O178">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P178">
+        <f t="shared" si="20"/>
+        <v>1.3187708224418652E-3</v>
+      </c>
+      <c r="Q178">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R178">
+        <f t="shared" si="22"/>
+        <v>6.6185810651301118</v>
+      </c>
+    </row>
+    <row r="179" spans="5:18" x14ac:dyDescent="0.2">
+      <c r="F179" t="s">
+        <v>56</v>
+      </c>
+      <c r="G179">
+        <v>60</v>
+      </c>
+      <c r="H179" s="8">
+        <v>430</v>
+      </c>
+      <c r="I179" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <f t="shared" si="37"/>
+        <v>7.9183708816000014</v>
+      </c>
+      <c r="N179">
+        <f t="shared" ref="N179" si="59">(M179 * (1 -U$141) + (0.04 * M179)) * ( 1 - AD$141 )</f>
+        <v>3.5917730318937608</v>
+      </c>
+      <c r="O179">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P179">
+        <f t="shared" si="20"/>
+        <v>2.1296398129073001E-3</v>
+      </c>
+      <c r="Q179">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R179">
+        <f t="shared" si="22"/>
+        <v>11.659777975667469</v>
+      </c>
+    </row>
+    <row r="180" spans="5:18" x14ac:dyDescent="0.2">
+      <c r="F180" t="s">
+        <v>57</v>
+      </c>
+      <c r="G180">
+        <v>65</v>
+      </c>
+      <c r="H180" s="8">
+        <v>440</v>
+      </c>
+      <c r="I180" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L180">
+        <v>1</v>
+      </c>
+      <c r="M180">
+        <f t="shared" si="37"/>
+        <v>8.0470938276000012</v>
+      </c>
+      <c r="N180">
+        <f t="shared" ref="N180" si="60">(M180 * (1 -V$141) + (0.04 * M180)) * ( 1 - AD$141 )</f>
+        <v>4.3261176417177598</v>
+      </c>
+      <c r="O180">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="P180">
+        <f t="shared" si="20"/>
+        <v>2.5650485939155208E-3</v>
+      </c>
+      <c r="Q180">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="R180">
+        <f t="shared" si="22"/>
+        <v>15.213944472661431</v>
       </c>
     </row>
   </sheetData>

--- a/packages/calculators/src/modules/test/4.1-beef.xlsx
+++ b/packages/calculators/src/modules/test/4.1-beef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{F3CF0DB7-189F-CB48-9787-EEC338E85ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{8FB9131E-94CA-3642-A0E7-6203DA3A4994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2920" yWindow="600" windowWidth="45460" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51080" yWindow="10420" windowWidth="28800" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.2.1 methane" sheetId="2" r:id="rId1"/>
